--- a/Markov Chain.xlsx
+++ b/Markov Chain.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Click\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Click\Desktop\کاتی و گرنگ\Hunar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB813E2-9F14-498D-BA64-11BE95E5D972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B79AC06-8852-4036-B1AD-64B30ED76CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{59F52203-B394-437A-9A5D-F6B5FDD0B84D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{59F52203-B394-437A-9A5D-F6B5FDD0B84D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Markov Chain" sheetId="2" r:id="rId1"/>
+    <sheet name="1st order Markov Chain" sheetId="2" r:id="rId1"/>
+    <sheet name="making it have equal count" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>year</t>
   </si>
@@ -100,6 +101,27 @@
   <si>
     <t>Classification</t>
   </si>
+  <si>
+    <t>0-490</t>
+  </si>
+  <si>
+    <t>490-640</t>
+  </si>
+  <si>
+    <t>640-780</t>
+  </si>
+  <si>
+    <t>780-880</t>
+  </si>
+  <si>
+    <t>880+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I balanced the definition to be all 20%, so any prediction close to 20% has little meaning. </t>
+  </si>
+  <si>
+    <t>Subtracting 20% from each prediction</t>
+  </si>
 </sst>
 </file>
 
@@ -108,7 +130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;د.ع.‏&quot;* #,##0.00_ ;_ &quot;د.ع.‏&quot;* \-#,##0.00_ ;_ &quot;د.ع.‏&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,8 +147,16 @@
       <charset val="178"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,6 +181,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -166,30 +202,45 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -508,770 +559,777 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B23E71-24D7-45A6-A9C7-B1A4A1DF1CC3}">
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="9" t="s">
+      <c r="H1" s="11"/>
+      <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="J1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1941</v>
       </c>
       <c r="B2">
         <v>780</v>
       </c>
-      <c r="C2" t="str">
-        <f>LOOKUP(B2,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C2" s="1" t="str">
+        <f t="shared" ref="C2:C33" si="0">LOOKUP(B2,$G$2:$G$6,$H$2:$H$6)</f>
         <v>good</v>
       </c>
-      <c r="H2">
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
         <v>2</v>
       </c>
-      <c r="J2">
-        <f>COUNTIF($C$2:$C$87,I2)</f>
+      <c r="I2">
+        <f>COUNTIF($C$2:$C$87,H2)</f>
         <v>5</v>
       </c>
-      <c r="K2" s="4">
-        <f>J2/SUM($J$2:$J$6)</f>
+      <c r="J2" s="2">
+        <f>I2/SUM($I$2:$I$6)</f>
         <v>5.8139534883720929E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1942</v>
       </c>
       <c r="B3">
         <v>470</v>
       </c>
-      <c r="C3" t="str">
-        <f>LOOKUP(B3,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="H3">
+      <c r="C3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="G3">
         <v>350</v>
       </c>
-      <c r="I3" t="s">
+      <c r="H3" t="s">
         <v>3</v>
       </c>
-      <c r="J3">
-        <f t="shared" ref="J3:J6" si="0">COUNTIF($C$2:$C$87,I3)</f>
+      <c r="I3">
+        <f t="shared" ref="I3:I6" si="1">COUNTIF($C$2:$C$87,H3)</f>
         <v>38</v>
       </c>
-      <c r="K3" s="4">
-        <f t="shared" ref="K3:K6" si="1">J3/SUM($J$2:$J$6)</f>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3:J6" si="2">I3/SUM($I$2:$I$6)</f>
         <v>0.44186046511627908</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1943</v>
       </c>
       <c r="B4">
         <v>690</v>
       </c>
-      <c r="C4" t="str">
-        <f>LOOKUP(B4,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="H4">
+      <c r="C4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="G4">
         <v>700</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" t="s">
         <v>4</v>
       </c>
-      <c r="J4">
-        <f t="shared" si="0"/>
+      <c r="I4">
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="K4" s="4">
-        <f t="shared" si="1"/>
+      <c r="J4" s="2">
+        <f t="shared" si="2"/>
         <v>0.2441860465116279</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1944</v>
       </c>
       <c r="B5">
         <v>640</v>
       </c>
-      <c r="C5" t="str">
-        <f>LOOKUP(B5,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="H5">
+      <c r="C5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="G5">
         <v>850</v>
       </c>
-      <c r="I5" t="s">
+      <c r="H5" t="s">
         <v>5</v>
       </c>
-      <c r="J5">
-        <f t="shared" si="0"/>
+      <c r="I5">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="K5" s="4">
-        <f t="shared" si="1"/>
+      <c r="J5" s="2">
+        <f t="shared" si="2"/>
         <v>0.19767441860465115</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1945</v>
       </c>
       <c r="B6">
         <v>790</v>
       </c>
-      <c r="C6" t="str">
-        <f>LOOKUP(B6,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C6" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>good</v>
       </c>
-      <c r="H6">
+      <c r="G6">
         <v>1000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="H6" t="s">
         <v>6</v>
       </c>
-      <c r="J6">
-        <f t="shared" si="0"/>
+      <c r="I6">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K6" s="4">
-        <f t="shared" si="1"/>
+      <c r="J6" s="2">
+        <f t="shared" si="2"/>
         <v>5.8139534883720929E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1946</v>
       </c>
       <c r="B7">
         <v>835</v>
       </c>
-      <c r="C7" t="str">
-        <f>LOOKUP(B7,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C7" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>good</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1947</v>
       </c>
       <c r="B8">
         <v>530</v>
       </c>
-      <c r="C8" t="str">
-        <f>LOOKUP(B8,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="C8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="H8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1948</v>
       </c>
       <c r="B9">
         <v>360</v>
       </c>
-      <c r="C9" t="str">
-        <f>LOOKUP(B9,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="H9" s="7" t="str" cm="1">
+        <f t="array" ref="H9:L9">TRANSPOSE($H$2:$H$6)</f>
+        <v>drought</v>
+      </c>
+      <c r="I9" s="6" t="str">
+        <v>normal</v>
+      </c>
+      <c r="J9" s="6" t="str">
+        <v>good</v>
+      </c>
+      <c r="K9" s="6" t="str">
+        <v>great</v>
+      </c>
+      <c r="L9" s="6" t="str">
+        <v>exceptional</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1949</v>
       </c>
       <c r="B10">
         <v>185</v>
       </c>
-      <c r="C10" t="str">
-        <f>LOOKUP(B10,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C10" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>drought</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="F10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="G10" s="5" t="str" cm="1">
+        <f t="array" ref="G10:G14">$H$2:$H$6</f>
+        <v>drought</v>
+      </c>
+      <c r="H10" cm="1">
+        <f t="array" ref="H10">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G10))</f>
         <v>2</v>
       </c>
       <c r="I10" cm="1">
-        <f t="array" ref="I10">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$H10))</f>
+        <f t="array" ref="I10">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G10))</f>
         <v>2</v>
       </c>
       <c r="J10" cm="1">
-        <f t="array" ref="J10">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$H10))</f>
-        <v>2</v>
+        <f t="array" ref="J10">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G10))</f>
+        <v>0</v>
       </c>
       <c r="K10" cm="1">
-        <f t="array" ref="K10">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$H10))</f>
+        <f t="array" ref="K10">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G10))</f>
+        <v>1</v>
+      </c>
+      <c r="L10" cm="1">
+        <f t="array" ref="L10">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G10))</f>
         <v>0</v>
       </c>
-      <c r="L10" cm="1">
-        <f t="array" ref="L10">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$H10))</f>
-        <v>1</v>
-      </c>
-      <c r="M10" cm="1">
-        <f t="array" ref="M10">SUM(($C$2:$C$100=M$9)*($C$3:$C$101=$H10))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1950</v>
       </c>
       <c r="B11">
         <v>40</v>
       </c>
-      <c r="C11" t="str">
-        <f>LOOKUP(B11,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>drought</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="9" t="s">
+      <c r="F11" s="10"/>
+      <c r="G11" s="5" t="str">
+        <v>normal</v>
+      </c>
+      <c r="H11" cm="1">
+        <f t="array" ref="H11">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G11))</f>
         <v>3</v>
       </c>
       <c r="I11" cm="1">
-        <f t="array" ref="I11">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$H11))</f>
-        <v>3</v>
+        <f t="array" ref="I11">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G11))</f>
+        <v>14</v>
       </c>
       <c r="J11" cm="1">
-        <f t="array" ref="J11">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$H11))</f>
-        <v>14</v>
+        <f t="array" ref="J11">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G11))</f>
+        <v>10</v>
       </c>
       <c r="K11" cm="1">
-        <f t="array" ref="K11">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$H11))</f>
-        <v>10</v>
+        <f t="array" ref="K11">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G11))</f>
+        <v>9</v>
       </c>
       <c r="L11" cm="1">
-        <f t="array" ref="L11">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$H11))</f>
-        <v>9</v>
-      </c>
-      <c r="M11" cm="1">
-        <f t="array" ref="M11">SUM(($C$2:$C$100=M$9)*($C$3:$C$101=$H11))</f>
+        <f t="array" ref="L11">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G11))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1951</v>
       </c>
       <c r="B12">
         <v>430</v>
       </c>
-      <c r="C12" t="str">
-        <f>LOOKUP(B12,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="9" t="s">
-        <v>4</v>
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="5" t="str">
+        <v>good</v>
+      </c>
+      <c r="H12" cm="1">
+        <f t="array" ref="H12">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G12))</f>
+        <v>0</v>
       </c>
       <c r="I12" cm="1">
-        <f t="array" ref="I12">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$H12))</f>
+        <f t="array" ref="I12">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G12))</f>
+        <v>13</v>
+      </c>
+      <c r="J12" cm="1">
+        <f t="array" ref="J12">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G12))</f>
+        <v>6</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G12))</f>
+        <v>1</v>
+      </c>
+      <c r="L12" cm="1">
+        <f t="array" ref="L12">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G12))</f>
         <v>0</v>
       </c>
-      <c r="J12" cm="1">
-        <f t="array" ref="J12">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$H12))</f>
-        <v>13</v>
-      </c>
-      <c r="K12" cm="1">
-        <f t="array" ref="K12">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$H12))</f>
-        <v>6</v>
-      </c>
-      <c r="L12" cm="1">
-        <f t="array" ref="L12">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$H12))</f>
-        <v>1</v>
-      </c>
-      <c r="M12" cm="1">
-        <f t="array" ref="M12">SUM(($C$2:$C$100=M$9)*($C$3:$C$101=$H12))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1952</v>
       </c>
       <c r="B13">
         <v>620</v>
       </c>
-      <c r="C13" t="str">
-        <f>LOOKUP(B13,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="9" t="s">
-        <v>5</v>
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="5" t="str">
+        <v>great</v>
+      </c>
+      <c r="H13" cm="1">
+        <f t="array" ref="H13">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G13))</f>
+        <v>0</v>
       </c>
       <c r="I13" cm="1">
-        <f t="array" ref="I13">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$H13))</f>
-        <v>0</v>
+        <f t="array" ref="I13">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G13))</f>
+        <v>7</v>
       </c>
       <c r="J13" cm="1">
-        <f t="array" ref="J13">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$H13))</f>
-        <v>7</v>
+        <f t="array" ref="J13">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G13))</f>
+        <v>4</v>
       </c>
       <c r="K13" cm="1">
-        <f t="array" ref="K13">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$H13))</f>
+        <f t="array" ref="K13">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G13))</f>
         <v>4</v>
       </c>
       <c r="L13" cm="1">
-        <f t="array" ref="L13">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$H13))</f>
-        <v>4</v>
-      </c>
-      <c r="M13" cm="1">
-        <f t="array" ref="M13">SUM(($C$2:$C$100=M$9)*($C$3:$C$101=$H13))</f>
+        <f t="array" ref="L13">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G13))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1953</v>
       </c>
       <c r="B14">
         <v>790</v>
       </c>
-      <c r="C14" t="str">
-        <f>LOOKUP(B14,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>good</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="9" t="s">
-        <v>6</v>
+      <c r="F14" s="10"/>
+      <c r="G14" s="5" t="str">
+        <v>exceptional</v>
+      </c>
+      <c r="H14" cm="1">
+        <f t="array" ref="H14">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G14))</f>
+        <v>0</v>
       </c>
       <c r="I14" cm="1">
-        <f t="array" ref="I14">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$H14))</f>
+        <f t="array" ref="I14">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G14))</f>
+        <v>2</v>
+      </c>
+      <c r="J14" cm="1">
+        <f t="array" ref="J14">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G14))</f>
+        <v>1</v>
+      </c>
+      <c r="K14" cm="1">
+        <f t="array" ref="K14">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G14))</f>
+        <v>2</v>
+      </c>
+      <c r="L14" cm="1">
+        <f t="array" ref="L14">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G14))</f>
         <v>0</v>
       </c>
-      <c r="J14" cm="1">
-        <f t="array" ref="J14">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$H14))</f>
-        <v>2</v>
-      </c>
-      <c r="K14" cm="1">
-        <f t="array" ref="K14">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$H14))</f>
-        <v>1</v>
-      </c>
-      <c r="L14" cm="1">
-        <f t="array" ref="L14">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$H14))</f>
-        <v>2</v>
-      </c>
-      <c r="M14" cm="1">
-        <f t="array" ref="M14">SUM(($C$2:$C$100=M$9)*($C$3:$C$101=$H14))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>1954</v>
       </c>
       <c r="B15">
         <v>880</v>
       </c>
-      <c r="C15" t="str">
-        <f>LOOKUP(B15,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C15" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>great</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1955</v>
       </c>
       <c r="B16">
         <v>560</v>
       </c>
-      <c r="C16" t="str">
-        <f>LOOKUP(B16,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1956</v>
       </c>
       <c r="B17">
         <v>455</v>
       </c>
-      <c r="C17" t="str">
-        <f>LOOKUP(B17,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="H17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>1957</v>
       </c>
       <c r="B18">
         <v>1240</v>
       </c>
-      <c r="C18" t="str">
-        <f>LOOKUP(B18,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>exceptional</v>
       </c>
-      <c r="G18" s="6">
+      <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H18" s="7" t="str" cm="1">
+        <f t="array" ref="H18:L18">TRANSPOSE($H$2:$H$6)</f>
+        <v>drought</v>
+      </c>
+      <c r="I18" s="6" t="str">
+        <v>normal</v>
+      </c>
+      <c r="J18" s="6" t="str">
+        <v>good</v>
+      </c>
+      <c r="K18" s="6" t="str">
+        <v>great</v>
+      </c>
+      <c r="L18" s="6" t="str">
+        <v>exceptional</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>1958</v>
       </c>
       <c r="B19">
         <v>410</v>
       </c>
-      <c r="C19" t="str">
-        <f>LOOKUP(B19,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="5">
-        <f>(I10+$G$18)/(SUM(I$10:I$14)+COUNT($I$10:$I$14)*$G$18)</f>
+      <c r="G19" s="5" t="str" cm="1">
+        <f t="array" ref="G19:G23">$H$2:$H$6</f>
+        <v>drought</v>
+      </c>
+      <c r="H19" s="3">
+        <f>(H10+$F$18)/(SUM(H$10:H$14)+COUNT($H$10:$H$14)*$F$18)</f>
         <v>0.4</v>
       </c>
-      <c r="J19" s="5">
-        <f t="shared" ref="J19:M19" si="2">(J10+$G$18)/(SUM(J$10:J$14)+COUNT($I$10:$I$14)*$G$18)</f>
+      <c r="I19" s="3">
+        <f t="shared" ref="I19:L19" si="3">(I10+$F$18)/(SUM(I$10:I$14)+COUNT($H$10:$H$14)*$F$18)</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="K19" s="5">
-        <f t="shared" si="2"/>
+      <c r="J19" s="3">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L19" s="5">
-        <f t="shared" si="2"/>
+      <c r="K19" s="3">
+        <f t="shared" si="3"/>
         <v>5.8823529411764705E-2</v>
       </c>
-      <c r="M19" s="5">
-        <f t="shared" si="2"/>
+      <c r="L19" s="3">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>1959</v>
       </c>
       <c r="B20">
         <v>580</v>
       </c>
-      <c r="C20" t="str">
-        <f>LOOKUP(B20,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" ref="I20:M20" si="3">(I11+$G$18)/(SUM(I$10:I$14)+COUNT($I$10:$I$14)*$G$18)</f>
+      <c r="C20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="5" t="str">
+        <v>normal</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" ref="H20:L20" si="4">(H11+$F$18)/(SUM(H$10:H$14)+COUNT($H$10:$H$14)*$F$18)</f>
         <v>0.6</v>
       </c>
-      <c r="J20" s="5">
-        <f t="shared" si="3"/>
+      <c r="I20" s="3">
+        <f t="shared" si="4"/>
         <v>0.36842105263157893</v>
       </c>
-      <c r="K20" s="5">
-        <f t="shared" si="3"/>
+      <c r="J20" s="3">
+        <f t="shared" si="4"/>
         <v>0.47619047619047616</v>
       </c>
-      <c r="L20" s="5">
-        <f t="shared" si="3"/>
+      <c r="K20" s="3">
+        <f t="shared" si="4"/>
         <v>0.52941176470588236</v>
       </c>
-      <c r="M20" s="5">
-        <f t="shared" si="3"/>
+      <c r="L20" s="3">
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>1960</v>
       </c>
       <c r="B21">
         <v>490</v>
       </c>
-      <c r="C21" t="str">
-        <f>LOOKUP(B21,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" ref="I21:M21" si="4">(I12+$G$18)/(SUM(I$10:I$14)+COUNT($I$10:$I$14)*$G$18)</f>
+      <c r="C21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="5" t="str">
+        <v>good</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" ref="H21:L21" si="5">(H12+$F$18)/(SUM(H$10:H$14)+COUNT($H$10:$H$14)*$F$18)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="5">
-        <f t="shared" si="4"/>
+      <c r="I21" s="3">
+        <f t="shared" si="5"/>
         <v>0.34210526315789475</v>
       </c>
-      <c r="K21" s="5">
-        <f t="shared" si="4"/>
+      <c r="J21" s="3">
+        <f t="shared" si="5"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="L21" s="5">
-        <f t="shared" si="4"/>
+      <c r="K21" s="3">
+        <f t="shared" si="5"/>
         <v>5.8823529411764705E-2</v>
       </c>
-      <c r="M21" s="5">
-        <f t="shared" si="4"/>
+      <c r="L21" s="3">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>1961</v>
       </c>
       <c r="B22">
         <v>820</v>
       </c>
-      <c r="C22" t="str">
-        <f>LOOKUP(B22,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C22" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>good</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" ref="I22:M22" si="5">(I13+$G$18)/(SUM(I$10:I$14)+COUNT($I$10:$I$14)*$G$18)</f>
+      <c r="F22" s="10"/>
+      <c r="G22" s="5" t="str">
+        <v>great</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" ref="H22:L22" si="6">(H13+$F$18)/(SUM(H$10:H$14)+COUNT($H$10:$H$14)*$F$18)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="5">
-        <f t="shared" si="5"/>
+      <c r="I22" s="3">
+        <f t="shared" si="6"/>
         <v>0.18421052631578946</v>
       </c>
-      <c r="K22" s="5">
-        <f t="shared" si="5"/>
+      <c r="J22" s="3">
+        <f t="shared" si="6"/>
         <v>0.19047619047619047</v>
       </c>
-      <c r="L22" s="5">
-        <f t="shared" si="5"/>
+      <c r="K22" s="3">
+        <f t="shared" si="6"/>
         <v>0.23529411764705882</v>
       </c>
-      <c r="M22" s="5">
-        <f t="shared" si="5"/>
+      <c r="L22" s="3">
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>1962</v>
       </c>
       <c r="B23">
         <v>530</v>
       </c>
-      <c r="C23" t="str">
-        <f>LOOKUP(B23,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" ref="I23:M23" si="6">(I14+$G$18)/(SUM(I$10:I$14)+COUNT($I$10:$I$14)*$G$18)</f>
+      <c r="C23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="5" t="str">
+        <v>exceptional</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" ref="H23:L23" si="7">(H14+$F$18)/(SUM(H$10:H$14)+COUNT($H$10:$H$14)*$F$18)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="5">
-        <f t="shared" si="6"/>
+      <c r="I23" s="3">
+        <f t="shared" si="7"/>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="K23" s="5">
-        <f t="shared" si="6"/>
+      <c r="J23" s="3">
+        <f t="shared" si="7"/>
         <v>4.7619047619047616E-2</v>
       </c>
-      <c r="L23" s="5">
-        <f t="shared" si="6"/>
+      <c r="K23" s="3">
+        <f t="shared" si="7"/>
         <v>0.11764705882352941</v>
       </c>
-      <c r="M23" s="5">
-        <f t="shared" si="6"/>
+      <c r="L23" s="3">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>1963</v>
       </c>
       <c r="B24">
         <v>980</v>
       </c>
-      <c r="C24" t="str">
-        <f>LOOKUP(B24,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C24" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>great</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1964</v>
       </c>
       <c r="B25">
         <v>490</v>
       </c>
-      <c r="C25" t="str">
-        <f>LOOKUP(B25,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>1965</v>
       </c>
       <c r="B26">
         <v>490</v>
       </c>
-      <c r="C26" t="str">
-        <f>LOOKUP(B26,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>1966</v>
       </c>
       <c r="B27">
         <v>385</v>
       </c>
-      <c r="C27" t="str">
-        <f>LOOKUP(B27,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>1967</v>
       </c>
       <c r="B28">
         <v>670</v>
       </c>
-      <c r="C28" t="str">
-        <f>LOOKUP(B28,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>1968</v>
       </c>
       <c r="B29">
         <v>795</v>
       </c>
-      <c r="C29" t="str">
-        <f>LOOKUP(B29,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C29" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>good</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>1969</v>
       </c>
       <c r="B30">
         <v>1135</v>
       </c>
-      <c r="C30" t="str">
-        <f>LOOKUP(B30,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C30" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>exceptional</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>1970</v>
       </c>
       <c r="B31">
         <v>430</v>
       </c>
-      <c r="C31" t="str">
-        <f>LOOKUP(B31,$H$2:$H$6,$I$2:$I$6)</f>
-        <v>normal</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1971</v>
       </c>
       <c r="B32">
         <v>770</v>
       </c>
-      <c r="C32" t="str">
-        <f>LOOKUP(B32,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C32" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>good</v>
       </c>
     </row>
@@ -1282,8 +1340,8 @@
       <c r="B33">
         <v>820</v>
       </c>
-      <c r="C33" t="str">
-        <f>LOOKUP(B33,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C33" s="1" t="str">
+        <f t="shared" si="0"/>
         <v>good</v>
       </c>
     </row>
@@ -1294,8 +1352,8 @@
       <c r="B34">
         <v>585</v>
       </c>
-      <c r="C34" t="str">
-        <f>LOOKUP(B34,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C34" s="1" t="str">
+        <f t="shared" ref="C34:C65" si="8">LOOKUP(B34,$G$2:$G$6,$H$2:$H$6)</f>
         <v>normal</v>
       </c>
     </row>
@@ -1306,8 +1364,8 @@
       <c r="B35">
         <v>995</v>
       </c>
-      <c r="C35" t="str">
-        <f>LOOKUP(B35,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C35" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1318,8 +1376,8 @@
       <c r="B36">
         <v>660</v>
       </c>
-      <c r="C36" t="str">
-        <f>LOOKUP(B36,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C36" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1330,8 +1388,8 @@
       <c r="B37">
         <v>750</v>
       </c>
-      <c r="C37" t="str">
-        <f>LOOKUP(B37,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C37" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1342,8 +1400,8 @@
       <c r="B38">
         <v>650</v>
       </c>
-      <c r="C38" t="str">
-        <f>LOOKUP(B38,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C38" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1354,8 +1412,8 @@
       <c r="B39">
         <v>700</v>
       </c>
-      <c r="C39" t="str">
-        <f>LOOKUP(B39,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C39" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1366,8 +1424,8 @@
       <c r="B40">
         <v>680</v>
       </c>
-      <c r="C40" t="str">
-        <f>LOOKUP(B40,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C40" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1378,8 +1436,8 @@
       <c r="B41">
         <v>570</v>
       </c>
-      <c r="C41" t="str">
-        <f>LOOKUP(B41,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C41" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1390,8 +1448,8 @@
       <c r="B42">
         <v>780</v>
       </c>
-      <c r="C42" t="str">
-        <f>LOOKUP(B42,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C42" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1402,8 +1460,8 @@
       <c r="B43">
         <v>970</v>
       </c>
-      <c r="C43" t="str">
-        <f>LOOKUP(B43,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C43" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1414,8 +1472,8 @@
       <c r="B44">
         <v>485</v>
       </c>
-      <c r="C44" t="str">
-        <f>LOOKUP(B44,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C44" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1426,8 +1484,8 @@
       <c r="B45">
         <v>705</v>
       </c>
-      <c r="C45" t="str">
-        <f>LOOKUP(B45,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C45" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1438,8 +1496,8 @@
       <c r="B46">
         <v>715</v>
       </c>
-      <c r="C46" t="str">
-        <f>LOOKUP(B46,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C46" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1450,8 +1508,8 @@
       <c r="B47">
         <v>725</v>
       </c>
-      <c r="C47" t="str">
-        <f>LOOKUP(B47,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C47" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1462,8 +1520,8 @@
       <c r="B48">
         <v>750</v>
       </c>
-      <c r="C48" t="str">
-        <f>LOOKUP(B48,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C48" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1474,8 +1532,8 @@
       <c r="B49">
         <v>902</v>
       </c>
-      <c r="C49" t="str">
-        <f>LOOKUP(B49,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C49" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1486,8 +1544,8 @@
       <c r="B50">
         <v>498</v>
       </c>
-      <c r="C50" t="str">
-        <f>LOOKUP(B50,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C50" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1498,8 +1556,8 @@
       <c r="B51">
         <v>945</v>
       </c>
-      <c r="C51" t="str">
-        <f>LOOKUP(B51,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C51" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1510,8 +1568,8 @@
       <c r="B52">
         <v>935</v>
       </c>
-      <c r="C52" t="str">
-        <f>LOOKUP(B52,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C52" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1522,8 +1580,8 @@
       <c r="B53">
         <v>1002</v>
       </c>
-      <c r="C53" t="str">
-        <f>LOOKUP(B53,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C53" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>exceptional</v>
       </c>
     </row>
@@ -1534,8 +1592,8 @@
       <c r="B54">
         <v>880</v>
       </c>
-      <c r="C54" t="str">
-        <f>LOOKUP(B54,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C54" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1546,8 +1604,8 @@
       <c r="B55">
         <v>960</v>
       </c>
-      <c r="C55" t="str">
-        <f>LOOKUP(B55,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C55" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1558,8 +1616,8 @@
       <c r="B56">
         <v>665</v>
       </c>
-      <c r="C56" t="str">
-        <f>LOOKUP(B56,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C56" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1570,8 +1628,8 @@
       <c r="B57">
         <v>780</v>
       </c>
-      <c r="C57" t="str">
-        <f>LOOKUP(B57,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C57" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1582,8 +1640,8 @@
       <c r="B58">
         <v>850</v>
       </c>
-      <c r="C58" t="str">
-        <f>LOOKUP(B58,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C58" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1594,8 +1652,8 @@
       <c r="B59">
         <v>620</v>
       </c>
-      <c r="C59" t="str">
-        <f>LOOKUP(B59,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C59" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1606,8 +1664,8 @@
       <c r="B60">
         <v>330</v>
       </c>
-      <c r="C60" t="str">
-        <f>LOOKUP(B60,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C60" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>drought</v>
       </c>
     </row>
@@ -1618,8 +1676,8 @@
       <c r="B61">
         <v>270</v>
       </c>
-      <c r="C61" t="str">
-        <f>LOOKUP(B61,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C61" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>drought</v>
       </c>
     </row>
@@ -1630,8 +1688,8 @@
       <c r="B62">
         <v>510</v>
       </c>
-      <c r="C62" t="str">
-        <f>LOOKUP(B62,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C62" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>normal</v>
       </c>
     </row>
@@ -1642,8 +1700,8 @@
       <c r="B63">
         <v>930</v>
       </c>
-      <c r="C63" t="str">
-        <f>LOOKUP(B63,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C63" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1654,8 +1712,8 @@
       <c r="B64">
         <v>875</v>
       </c>
-      <c r="C64" t="str">
-        <f>LOOKUP(B64,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C64" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>great</v>
       </c>
     </row>
@@ -1666,8 +1724,8 @@
       <c r="B65">
         <v>840</v>
       </c>
-      <c r="C65" t="str">
-        <f>LOOKUP(B65,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C65" s="1" t="str">
+        <f t="shared" si="8"/>
         <v>good</v>
       </c>
     </row>
@@ -1678,8 +1736,8 @@
       <c r="B66">
         <v>630</v>
       </c>
-      <c r="C66" t="str">
-        <f>LOOKUP(B66,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C66" s="1" t="str">
+        <f t="shared" ref="C66:C87" si="9">LOOKUP(B66,$G$2:$G$6,$H$2:$H$6)</f>
         <v>normal</v>
       </c>
     </row>
@@ -1690,8 +1748,8 @@
       <c r="B67">
         <v>875</v>
       </c>
-      <c r="C67" t="str">
-        <f>LOOKUP(B67,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C67" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>great</v>
       </c>
     </row>
@@ -1702,8 +1760,8 @@
       <c r="B68">
         <v>874</v>
       </c>
-      <c r="C68" t="str">
-        <f>LOOKUP(B68,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C68" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>great</v>
       </c>
     </row>
@@ -1714,8 +1772,8 @@
       <c r="B69">
         <v>307</v>
       </c>
-      <c r="C69" t="str">
-        <f>LOOKUP(B69,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C69" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>drought</v>
       </c>
     </row>
@@ -1726,8 +1784,8 @@
       <c r="B70">
         <v>415</v>
       </c>
-      <c r="C70" t="str">
-        <f>LOOKUP(B70,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C70" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1738,8 +1796,8 @@
       <c r="B71">
         <v>844</v>
       </c>
-      <c r="C71" t="str">
-        <f>LOOKUP(B71,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C71" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>good</v>
       </c>
     </row>
@@ -1750,8 +1808,8 @@
       <c r="B72">
         <v>661</v>
       </c>
-      <c r="C72" t="str">
-        <f>LOOKUP(B72,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C72" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1762,8 +1820,8 @@
       <c r="B73">
         <v>547</v>
       </c>
-      <c r="C73" t="str">
-        <f>LOOKUP(B73,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C73" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1774,8 +1832,8 @@
       <c r="B74">
         <v>826</v>
       </c>
-      <c r="C74" t="str">
-        <f>LOOKUP(B74,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C74" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>good</v>
       </c>
     </row>
@@ -1786,8 +1844,8 @@
       <c r="B75">
         <v>581</v>
       </c>
-      <c r="C75" t="str">
-        <f>LOOKUP(B75,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C75" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1798,8 +1856,8 @@
       <c r="B76">
         <v>691</v>
       </c>
-      <c r="C76" t="str">
-        <f>LOOKUP(B76,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C76" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1810,8 +1868,8 @@
       <c r="B77">
         <v>947</v>
       </c>
-      <c r="C77" t="str">
-        <f>LOOKUP(B77,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C77" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>great</v>
       </c>
     </row>
@@ -1822,8 +1880,8 @@
       <c r="B78">
         <v>561</v>
       </c>
-      <c r="C78" t="str">
-        <f>LOOKUP(B78,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C78" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1834,8 +1892,8 @@
       <c r="B79">
         <v>850</v>
       </c>
-      <c r="C79" t="str">
-        <f>LOOKUP(B79,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C79" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>great</v>
       </c>
     </row>
@@ -1846,8 +1904,8 @@
       <c r="B80">
         <v>1618</v>
       </c>
-      <c r="C80" t="str">
-        <f>LOOKUP(B80,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C80" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>exceptional</v>
       </c>
     </row>
@@ -1858,8 +1916,8 @@
       <c r="B81">
         <v>931</v>
       </c>
-      <c r="C81" t="str">
-        <f>LOOKUP(B81,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C81" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>great</v>
       </c>
     </row>
@@ -1870,8 +1928,8 @@
       <c r="B82">
         <v>401</v>
       </c>
-      <c r="C82" t="str">
-        <f>LOOKUP(B82,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C82" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1882,8 +1940,8 @@
       <c r="B83">
         <v>420</v>
       </c>
-      <c r="C83" t="str">
-        <f>LOOKUP(B83,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C83" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1894,8 +1952,8 @@
       <c r="B84">
         <v>781</v>
       </c>
-      <c r="C84" t="str">
-        <f>LOOKUP(B84,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C84" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>good</v>
       </c>
     </row>
@@ -1906,8 +1964,8 @@
       <c r="B85">
         <v>724</v>
       </c>
-      <c r="C85" t="str">
-        <f>LOOKUP(B85,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C85" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>good</v>
       </c>
     </row>
@@ -1918,8 +1976,8 @@
       <c r="B86">
         <v>350</v>
       </c>
-      <c r="C86" t="str">
-        <f>LOOKUP(B86,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C86" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>normal</v>
       </c>
     </row>
@@ -1930,19 +1988,1658 @@
       <c r="B87">
         <v>1070</v>
       </c>
-      <c r="C87" t="str">
-        <f>LOOKUP(B87,$H$2:$H$6,$I$2:$I$6)</f>
+      <c r="C87" s="1" t="str">
+        <f t="shared" si="9"/>
         <v>exceptional</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="G19:G23"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="G10:G14"/>
-    <mergeCell ref="I17:M17"/>
+    <mergeCell ref="F19:F23"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="F10:F14"/>
+    <mergeCell ref="H17:L17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{429F57A1-FABB-42F2-843F-7AF5619669EC}">
+  <dimension ref="A1:Q87"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1941</v>
+      </c>
+      <c r="B2">
+        <v>780</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f t="shared" ref="C2:C65" si="0">LOOKUP(B2,$G$2:$G$6,$H$2:$H$6)</f>
+        <v>780-880</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF($C$2:$C$87,H2)</f>
+        <v>17</v>
+      </c>
+      <c r="J2" s="3">
+        <f>I2/SUM($I$2:$I$6)</f>
+        <v>0.19767441860465115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1942</v>
+      </c>
+      <c r="B3">
+        <v>470</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="G3">
+        <v>490</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I6" si="1">COUNTIF($C$2:$C$87,H3)</f>
+        <v>17</v>
+      </c>
+      <c r="J3" s="3">
+        <f t="shared" ref="J3:J6" si="2">I3/SUM($I$2:$I$6)</f>
+        <v>0.19767441860465115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1943</v>
+      </c>
+      <c r="B4">
+        <v>690</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+      <c r="G4">
+        <v>640</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="J4" s="3">
+        <f t="shared" si="2"/>
+        <v>0.19767441860465115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1944</v>
+      </c>
+      <c r="B5">
+        <v>640</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+      <c r="G5">
+        <v>780</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="J5" s="3">
+        <f t="shared" si="2"/>
+        <v>0.20930232558139536</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>1945</v>
+      </c>
+      <c r="B6">
+        <v>790</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+      <c r="G6">
+        <v>880</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.19767441860465115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>1946</v>
+      </c>
+      <c r="B7">
+        <v>835</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1947</v>
+      </c>
+      <c r="B8">
+        <v>530</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>1948</v>
+      </c>
+      <c r="B9">
+        <v>360</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="H9" s="7" t="str" cm="1">
+        <f t="array" ref="H9:L9">TRANSPOSE($H$2:$H$6)</f>
+        <v>0-490</v>
+      </c>
+      <c r="I9" s="7" t="str">
+        <v>490-640</v>
+      </c>
+      <c r="J9" s="7" t="str">
+        <v>640-780</v>
+      </c>
+      <c r="K9" s="7" t="str">
+        <v>780-880</v>
+      </c>
+      <c r="L9" s="7" t="str">
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>1949</v>
+      </c>
+      <c r="B10">
+        <v>185</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="5" t="str" cm="1">
+        <f t="array" ref="G10:G14">$H$2:$H$6</f>
+        <v>0-490</v>
+      </c>
+      <c r="H10" cm="1">
+        <f t="array" ref="H10">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G10))</f>
+        <v>6</v>
+      </c>
+      <c r="I10" cm="1">
+        <f t="array" ref="I10">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G10))</f>
+        <v>4</v>
+      </c>
+      <c r="J10" cm="1">
+        <f t="array" ref="J10">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G10))</f>
+        <v>1</v>
+      </c>
+      <c r="K10" cm="1">
+        <f t="array" ref="K10">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G10))</f>
+        <v>2</v>
+      </c>
+      <c r="L10" cm="1">
+        <f t="array" ref="L10">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G10))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>1950</v>
+      </c>
+      <c r="B11">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="5" t="str">
+        <v>490-640</v>
+      </c>
+      <c r="H11" cm="1">
+        <f t="array" ref="H11">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G11))</f>
+        <v>3</v>
+      </c>
+      <c r="I11" cm="1">
+        <f t="array" ref="I11">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G11))</f>
+        <v>2</v>
+      </c>
+      <c r="J11" cm="1">
+        <f t="array" ref="J11">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G11))</f>
+        <v>2</v>
+      </c>
+      <c r="K11" cm="1">
+        <f t="array" ref="K11">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G11))</f>
+        <v>6</v>
+      </c>
+      <c r="L11" cm="1">
+        <f t="array" ref="L11">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G11))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>1951</v>
+      </c>
+      <c r="B12">
+        <v>430</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="5" t="str">
+        <v>640-780</v>
+      </c>
+      <c r="H12" cm="1">
+        <f t="array" ref="H12">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G12))</f>
+        <v>4</v>
+      </c>
+      <c r="I12" cm="1">
+        <f t="array" ref="I12">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G12))</f>
+        <v>1</v>
+      </c>
+      <c r="J12" cm="1">
+        <f t="array" ref="J12">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G12))</f>
+        <v>8</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G12))</f>
+        <v>2</v>
+      </c>
+      <c r="L12" cm="1">
+        <f t="array" ref="L12">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G12))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>1952</v>
+      </c>
+      <c r="B13">
+        <v>620</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="5" t="str">
+        <v>780-880</v>
+      </c>
+      <c r="H13" cm="1">
+        <f t="array" ref="H13">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G13))</f>
+        <v>2</v>
+      </c>
+      <c r="I13" cm="1">
+        <f t="array" ref="I13">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G13))</f>
+        <v>6</v>
+      </c>
+      <c r="J13" cm="1">
+        <f t="array" ref="J13">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G13))</f>
+        <v>4</v>
+      </c>
+      <c r="K13" cm="1">
+        <f t="array" ref="K13">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G13))</f>
+        <v>4</v>
+      </c>
+      <c r="L13" cm="1">
+        <f t="array" ref="L13">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G13))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>1953</v>
+      </c>
+      <c r="B14">
+        <v>790</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="5" t="str">
+        <v>880+</v>
+      </c>
+      <c r="H14" cm="1">
+        <f t="array" ref="H14">SUM(($C$2:$C$100=H$9)*($C$3:$C$101=$G14))</f>
+        <v>2</v>
+      </c>
+      <c r="I14" cm="1">
+        <f t="array" ref="I14">SUM(($C$2:$C$100=I$9)*($C$3:$C$101=$G14))</f>
+        <v>4</v>
+      </c>
+      <c r="J14" cm="1">
+        <f t="array" ref="J14">SUM(($C$2:$C$100=J$9)*($C$3:$C$101=$G14))</f>
+        <v>2</v>
+      </c>
+      <c r="K14" cm="1">
+        <f t="array" ref="K14">SUM(($C$2:$C$100=K$9)*($C$3:$C$101=$G14))</f>
+        <v>4</v>
+      </c>
+      <c r="L14" cm="1">
+        <f t="array" ref="L14">SUM(($C$2:$C$100=L$9)*($C$3:$C$101=$G14))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>1954</v>
+      </c>
+      <c r="B15">
+        <v>880</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1955</v>
+      </c>
+      <c r="B16">
+        <v>560</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>1956</v>
+      </c>
+      <c r="B17">
+        <v>455</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="H17" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1957</v>
+      </c>
+      <c r="B18">
+        <v>1240</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="H18" s="7" t="str" cm="1">
+        <f t="array" ref="H18:L18">TRANSPOSE($H$2:$H$6)</f>
+        <v>0-490</v>
+      </c>
+      <c r="I18" s="7" t="str">
+        <v>490-640</v>
+      </c>
+      <c r="J18" s="7" t="str">
+        <v>640-780</v>
+      </c>
+      <c r="K18" s="7" t="str">
+        <v>780-880</v>
+      </c>
+      <c r="L18" s="7" t="str">
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>1958</v>
+      </c>
+      <c r="B19">
+        <v>410</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="5" t="str" cm="1">
+        <f t="array" ref="G19:G23">$H$2:$H$6</f>
+        <v>0-490</v>
+      </c>
+      <c r="H19" s="3">
+        <f>H10/SUM(H$10:H$14)</f>
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" ref="I19:L19" si="3">I10/SUM(I$10:I$14)</f>
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="J19" s="3">
+        <f t="shared" si="3"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="3"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L19" s="3">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>1959</v>
+      </c>
+      <c r="B20">
+        <v>580</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="5" t="str">
+        <v>490-640</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" ref="H20:L20" si="4">H11/SUM(H$10:H$14)</f>
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="4"/>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="J20" s="3">
+        <f t="shared" si="4"/>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="K20" s="3">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L20" s="3">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>1960</v>
+      </c>
+      <c r="B21">
+        <v>490</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="5" t="str">
+        <v>640-780</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" ref="H21:L21" si="5">H12/SUM(H$10:H$14)</f>
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="5"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J21" s="3">
+        <f t="shared" si="5"/>
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="K21" s="3">
+        <f t="shared" si="5"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L21" s="3">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>1961</v>
+      </c>
+      <c r="B22">
+        <v>820</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="5" t="str">
+        <v>780-880</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" ref="H22:L22" si="6">H13/SUM(H$10:H$14)</f>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="6"/>
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="J22" s="3">
+        <f t="shared" si="6"/>
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="6"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="6"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>1962</v>
+      </c>
+      <c r="B23">
+        <v>530</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="5" t="str">
+        <v>880+</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" ref="H23:L23" si="7">H14/SUM(H$10:H$14)</f>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="7"/>
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" si="7"/>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="K23" s="3">
+        <f t="shared" si="7"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="7"/>
+        <v>0.3125</v>
+      </c>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>1963</v>
+      </c>
+      <c r="B24">
+        <v>980</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>1964</v>
+      </c>
+      <c r="B25">
+        <v>490</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>1965</v>
+      </c>
+      <c r="B26">
+        <v>490</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="H26" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>1966</v>
+      </c>
+      <c r="B27">
+        <v>385</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="H27" s="7" t="str" cm="1">
+        <f t="array" ref="H27:L27">TRANSPOSE($H$2:$H$6)</f>
+        <v>0-490</v>
+      </c>
+      <c r="I27" s="7" t="str">
+        <v>490-640</v>
+      </c>
+      <c r="J27" s="7" t="str">
+        <v>640-780</v>
+      </c>
+      <c r="K27" s="7" t="str">
+        <v>780-880</v>
+      </c>
+      <c r="L27" s="7" t="str">
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>1967</v>
+      </c>
+      <c r="B28">
+        <v>670</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="5" t="str" cm="1">
+        <f t="array" ref="G28:G32">$H$2:$H$6</f>
+        <v>0-490</v>
+      </c>
+      <c r="H28" s="3">
+        <f>H10/SUM(H$10:H$14)-0.2</f>
+        <v>0.15294117647058825</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" ref="I28:L28" si="8">I10/SUM(I$10:I$14)-0.2</f>
+        <v>3.5294117647058809E-2</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" si="8"/>
+        <v>-0.14117647058823529</v>
+      </c>
+      <c r="K28" s="3">
+        <f t="shared" si="8"/>
+        <v>-8.8888888888888906E-2</v>
+      </c>
+      <c r="L28" s="3">
+        <f t="shared" si="8"/>
+        <v>4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>1968</v>
+      </c>
+      <c r="B29">
+        <v>795</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="5" t="str">
+        <v>490-640</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" ref="H29:L29" si="9">H11/SUM(H$10:H$14)-0.2</f>
+        <v>-2.3529411764705882E-2</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="9"/>
+        <v>-8.2352941176470601E-2</v>
+      </c>
+      <c r="J29" s="3">
+        <f t="shared" si="9"/>
+        <v>-8.2352941176470601E-2</v>
+      </c>
+      <c r="K29" s="3">
+        <f t="shared" si="9"/>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="L29" s="3">
+        <f t="shared" si="9"/>
+        <v>4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>1969</v>
+      </c>
+      <c r="B30">
+        <v>1135</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="5" t="str">
+        <v>640-780</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" ref="H30:L30" si="10">H12/SUM(H$10:H$14)-0.2</f>
+        <v>3.5294117647058809E-2</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="10"/>
+        <v>-0.14117647058823529</v>
+      </c>
+      <c r="J30" s="3">
+        <f t="shared" si="10"/>
+        <v>0.27058823529411763</v>
+      </c>
+      <c r="K30" s="3">
+        <f t="shared" si="10"/>
+        <v>-8.8888888888888906E-2</v>
+      </c>
+      <c r="L30" s="3">
+        <f t="shared" si="10"/>
+        <v>-7.5000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>1970</v>
+      </c>
+      <c r="B31">
+        <v>430</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+      <c r="F31" s="10"/>
+      <c r="G31" s="5" t="str">
+        <v>780-880</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" ref="H31:L31" si="11">H13/SUM(H$10:H$14)-0.2</f>
+        <v>-8.2352941176470601E-2</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="11"/>
+        <v>0.15294117647058825</v>
+      </c>
+      <c r="J31" s="3">
+        <f t="shared" si="11"/>
+        <v>3.5294117647058809E-2</v>
+      </c>
+      <c r="K31" s="3">
+        <f t="shared" si="11"/>
+        <v>2.2222222222222199E-2</v>
+      </c>
+      <c r="L31" s="3">
+        <f t="shared" si="11"/>
+        <v>-0.13750000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>1971</v>
+      </c>
+      <c r="B32">
+        <v>770</v>
+      </c>
+      <c r="C32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="5" t="str">
+        <v>880+</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" ref="H32:L32" si="12">H14/SUM(H$10:H$14)-0.2</f>
+        <v>-8.2352941176470601E-2</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="12"/>
+        <v>3.5294117647058809E-2</v>
+      </c>
+      <c r="J32" s="3">
+        <f t="shared" si="12"/>
+        <v>-8.2352941176470601E-2</v>
+      </c>
+      <c r="K32" s="3">
+        <f t="shared" si="12"/>
+        <v>2.2222222222222199E-2</v>
+      </c>
+      <c r="L32" s="3">
+        <f t="shared" si="12"/>
+        <v>0.11249999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>1972</v>
+      </c>
+      <c r="B33">
+        <v>820</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>1973</v>
+      </c>
+      <c r="B34">
+        <v>585</v>
+      </c>
+      <c r="C34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>1974</v>
+      </c>
+      <c r="B35">
+        <v>995</v>
+      </c>
+      <c r="C35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>1975</v>
+      </c>
+      <c r="B36">
+        <v>660</v>
+      </c>
+      <c r="C36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>1976</v>
+      </c>
+      <c r="B37">
+        <v>750</v>
+      </c>
+      <c r="C37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>1977</v>
+      </c>
+      <c r="B38">
+        <v>650</v>
+      </c>
+      <c r="C38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>1978</v>
+      </c>
+      <c r="B39">
+        <v>700</v>
+      </c>
+      <c r="C39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B40">
+        <v>680</v>
+      </c>
+      <c r="C40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B41">
+        <v>570</v>
+      </c>
+      <c r="C41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B42">
+        <v>780</v>
+      </c>
+      <c r="C42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B43">
+        <v>970</v>
+      </c>
+      <c r="C43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B44">
+        <v>485</v>
+      </c>
+      <c r="C44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>1984</v>
+      </c>
+      <c r="B45">
+        <v>705</v>
+      </c>
+      <c r="C45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>1985</v>
+      </c>
+      <c r="B46">
+        <v>715</v>
+      </c>
+      <c r="C46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>1986</v>
+      </c>
+      <c r="B47">
+        <v>725</v>
+      </c>
+      <c r="C47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>1987</v>
+      </c>
+      <c r="B48">
+        <v>750</v>
+      </c>
+      <c r="C48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>1988</v>
+      </c>
+      <c r="B49">
+        <v>902</v>
+      </c>
+      <c r="C49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>1989</v>
+      </c>
+      <c r="B50">
+        <v>498</v>
+      </c>
+      <c r="C50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>1990</v>
+      </c>
+      <c r="B51">
+        <v>945</v>
+      </c>
+      <c r="C51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>1991</v>
+      </c>
+      <c r="B52">
+        <v>935</v>
+      </c>
+      <c r="C52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>1992</v>
+      </c>
+      <c r="B53">
+        <v>1002</v>
+      </c>
+      <c r="C53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>1993</v>
+      </c>
+      <c r="B54">
+        <v>880</v>
+      </c>
+      <c r="C54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>1994</v>
+      </c>
+      <c r="B55">
+        <v>960</v>
+      </c>
+      <c r="C55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>1995</v>
+      </c>
+      <c r="B56">
+        <v>665</v>
+      </c>
+      <c r="C56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>1996</v>
+      </c>
+      <c r="B57">
+        <v>780</v>
+      </c>
+      <c r="C57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>1997</v>
+      </c>
+      <c r="B58">
+        <v>850</v>
+      </c>
+      <c r="C58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>1998</v>
+      </c>
+      <c r="B59">
+        <v>620</v>
+      </c>
+      <c r="C59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>1999</v>
+      </c>
+      <c r="B60">
+        <v>330</v>
+      </c>
+      <c r="C60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B61">
+        <v>270</v>
+      </c>
+      <c r="C61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B62">
+        <v>510</v>
+      </c>
+      <c r="C62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>2002</v>
+      </c>
+      <c r="B63">
+        <v>930</v>
+      </c>
+      <c r="C63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>2003</v>
+      </c>
+      <c r="B64">
+        <v>875</v>
+      </c>
+      <c r="C64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>2004</v>
+      </c>
+      <c r="B65">
+        <v>840</v>
+      </c>
+      <c r="C65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B66">
+        <v>630</v>
+      </c>
+      <c r="C66" s="1" t="str">
+        <f t="shared" ref="C66:C87" si="13">LOOKUP(B66,$G$2:$G$6,$H$2:$H$6)</f>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B67">
+        <v>875</v>
+      </c>
+      <c r="C67" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B68">
+        <v>874</v>
+      </c>
+      <c r="C68" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B69">
+        <v>307</v>
+      </c>
+      <c r="C69" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B70">
+        <v>415</v>
+      </c>
+      <c r="C70" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>2010</v>
+      </c>
+      <c r="B71">
+        <v>844</v>
+      </c>
+      <c r="C71" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>2011</v>
+      </c>
+      <c r="B72">
+        <v>661</v>
+      </c>
+      <c r="C72" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>2012</v>
+      </c>
+      <c r="B73">
+        <v>547</v>
+      </c>
+      <c r="C73" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>2013</v>
+      </c>
+      <c r="B74">
+        <v>826</v>
+      </c>
+      <c r="C74" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>2014</v>
+      </c>
+      <c r="B75">
+        <v>581</v>
+      </c>
+      <c r="C75" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>2015</v>
+      </c>
+      <c r="B76">
+        <v>691</v>
+      </c>
+      <c r="C76" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>2016</v>
+      </c>
+      <c r="B77">
+        <v>947</v>
+      </c>
+      <c r="C77" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>2017</v>
+      </c>
+      <c r="B78">
+        <v>561</v>
+      </c>
+      <c r="C78" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>490-640</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>2018</v>
+      </c>
+      <c r="B79">
+        <v>850</v>
+      </c>
+      <c r="C79" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>2019</v>
+      </c>
+      <c r="B80">
+        <v>1618</v>
+      </c>
+      <c r="C80" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B81">
+        <v>931</v>
+      </c>
+      <c r="C81" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>880+</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B82">
+        <v>401</v>
+      </c>
+      <c r="C82" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B83">
+        <v>420</v>
+      </c>
+      <c r="C83" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B84">
+        <v>781</v>
+      </c>
+      <c r="C84" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>780-880</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B85">
+        <v>724</v>
+      </c>
+      <c r="C85" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>640-780</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B86">
+        <v>350</v>
+      </c>
+      <c r="C86" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>0-490</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B87">
+        <v>1070</v>
+      </c>
+      <c r="C87" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>880+</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="H26:L26"/>
+    <mergeCell ref="F28:F32"/>
+    <mergeCell ref="F25:L25"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="F10:F14"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="F19:F23"/>
+    <mergeCell ref="N19:Q23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H28:L32">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Markov Chain.xlsx
+++ b/Markov Chain.xlsx
@@ -8,14 +8,59 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Click\Desktop\کاتی و گرنگ\Hunar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B79AC06-8852-4036-B1AD-64B30ED76CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D59567-A274-44BE-88D2-7631B957752B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{59F52203-B394-437A-9A5D-F6B5FDD0B84D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{59F52203-B394-437A-9A5D-F6B5FDD0B84D}"/>
   </bookViews>
   <sheets>
     <sheet name="1st order Markov Chain" sheetId="2" r:id="rId1"/>
     <sheet name="making it have equal count" sheetId="3" r:id="rId2"/>
+    <sheet name="2nd order" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'2nd order'!$G$3:$G$6</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'2nd order'!$G$3</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'2nd order'!$G$3</definedName>
+    <definedName name="solver_lhs3" localSheetId="2" hidden="1">'2nd order'!$G$4</definedName>
+    <definedName name="solver_lhs4" localSheetId="2" hidden="1">'2nd order'!$G$5</definedName>
+    <definedName name="solver_lhs5" localSheetId="2" hidden="1">'2nd order'!$G$6</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.75</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">5</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'2nd order'!$R$14</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.00001</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'2nd order'!$G$4</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">50</definedName>
+    <definedName name="solver_rhs3" localSheetId="2" hidden="1">'2nd order'!$G$5</definedName>
+    <definedName name="solver_rhs4" localSheetId="2" hidden="1">'2nd order'!$G$6</definedName>
+    <definedName name="solver_rhs5" localSheetId="2" hidden="1">1000</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">1000</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">900</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +81,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>year</t>
   </si>
@@ -122,15 +167,43 @@
   <si>
     <t>Subtracting 20% from each prediction</t>
   </si>
+  <si>
+    <t>Definition2</t>
+  </si>
+  <si>
+    <t>aim</t>
+  </si>
+  <si>
+    <t>[0-273]</t>
+  </si>
+  <si>
+    <t>[273-552]</t>
+  </si>
+  <si>
+    <t>[552-720]</t>
+  </si>
+  <si>
+    <t>[720-875]</t>
+  </si>
+  <si>
+    <t>[875+]</t>
+  </si>
+  <si>
+    <t>next year</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_ &quot;د.ع.‏&quot;* #,##0.00_ ;_ &quot;د.ع.‏&quot;* \-#,##0.00_ ;_ &quot;د.ع.‏&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +226,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -202,7 +290,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +313,12 @@
     <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -234,15 +328,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -582,10 +678,10 @@
       <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="11"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
@@ -746,13 +842,13 @@
         <f t="shared" si="0"/>
         <v>normal</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -793,7 +889,7 @@
         <f t="shared" si="0"/>
         <v>drought</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="5" t="str" cm="1">
@@ -832,7 +928,7 @@
         <f t="shared" si="0"/>
         <v>drought</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="12"/>
       <c r="G11" s="5" t="str">
         <v>normal</v>
       </c>
@@ -868,7 +964,7 @@
         <f t="shared" si="0"/>
         <v>normal</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="5" t="str">
         <v>good</v>
       </c>
@@ -904,7 +1000,7 @@
         <f t="shared" si="0"/>
         <v>normal</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="5" t="str">
         <v>great</v>
       </c>
@@ -940,7 +1036,7 @@
         <f t="shared" si="0"/>
         <v>good</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="5" t="str">
         <v>exceptional</v>
       </c>
@@ -1003,13 +1099,13 @@
       <c r="F17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1053,7 +1149,7 @@
         <f t="shared" si="0"/>
         <v>normal</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="12" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="5" t="str" cm="1">
@@ -1092,7 +1188,7 @@
         <f t="shared" si="0"/>
         <v>normal</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="5" t="str">
         <v>normal</v>
       </c>
@@ -1128,7 +1224,7 @@
         <f t="shared" si="0"/>
         <v>normal</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="5" t="str">
         <v>good</v>
       </c>
@@ -1164,7 +1260,7 @@
         <f t="shared" si="0"/>
         <v>good</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="5" t="str">
         <v>great</v>
       </c>
@@ -1200,7 +1296,7 @@
         <f t="shared" si="0"/>
         <v>normal</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="5" t="str">
         <v>exceptional</v>
       </c>
@@ -2030,10 +2126,10 @@
       <c r="C1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="11"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
@@ -2194,13 +2290,13 @@
         <f t="shared" si="0"/>
         <v>490-640</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2241,7 +2337,7 @@
         <f t="shared" si="0"/>
         <v>0-490</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="5" t="str" cm="1">
@@ -2280,7 +2376,7 @@
         <f t="shared" si="0"/>
         <v>0-490</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="12"/>
       <c r="G11" s="5" t="str">
         <v>490-640</v>
       </c>
@@ -2316,7 +2412,7 @@
         <f t="shared" si="0"/>
         <v>0-490</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="5" t="str">
         <v>640-780</v>
       </c>
@@ -2352,7 +2448,7 @@
         <f t="shared" si="0"/>
         <v>490-640</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="5" t="str">
         <v>780-880</v>
       </c>
@@ -2388,7 +2484,7 @@
         <f t="shared" si="0"/>
         <v>780-880</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="5" t="str">
         <v>880+</v>
       </c>
@@ -2448,14 +2544,14 @@
         <f t="shared" si="0"/>
         <v>0-490</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="H17" s="12" t="s">
+      <c r="F17" s="10"/>
+      <c r="H17" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -2468,7 +2564,7 @@
         <f t="shared" si="0"/>
         <v>880+</v>
       </c>
-      <c r="F18" s="13"/>
+      <c r="F18" s="10"/>
       <c r="H18" s="7" t="str" cm="1">
         <f t="array" ref="H18:L18">TRANSPOSE($H$2:$H$6)</f>
         <v>0-490</v>
@@ -2497,7 +2593,7 @@
         <f t="shared" si="0"/>
         <v>0-490</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="12" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="5" t="str" cm="1">
@@ -2524,12 +2620,12 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="N19" s="14" t="s">
+      <c r="N19" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -2542,7 +2638,7 @@
         <f t="shared" si="0"/>
         <v>490-640</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="5" t="str">
         <v>490-640</v>
       </c>
@@ -2566,10 +2662,10 @@
         <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -2582,7 +2678,7 @@
         <f t="shared" si="0"/>
         <v>490-640</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="5" t="str">
         <v>640-780</v>
       </c>
@@ -2606,10 +2702,10 @@
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -2622,7 +2718,7 @@
         <f t="shared" si="0"/>
         <v>780-880</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="5" t="str">
         <v>780-880</v>
       </c>
@@ -2646,10 +2742,10 @@
         <f t="shared" si="6"/>
         <v>6.25E-2</v>
       </c>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -2662,7 +2758,7 @@
         <f t="shared" si="0"/>
         <v>490-640</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="5" t="str">
         <v>880+</v>
       </c>
@@ -2686,10 +2782,10 @@
         <f t="shared" si="7"/>
         <v>0.3125</v>
       </c>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -2714,15 +2810,15 @@
         <f t="shared" si="0"/>
         <v>490-640</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -2735,14 +2831,14 @@
         <f t="shared" si="0"/>
         <v>490-640</v>
       </c>
-      <c r="F26" s="13"/>
-      <c r="H26" s="12" t="s">
+      <c r="F26" s="10"/>
+      <c r="H26" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -2755,7 +2851,7 @@
         <f t="shared" si="0"/>
         <v>0-490</v>
       </c>
-      <c r="F27" s="13"/>
+      <c r="F27" s="10"/>
       <c r="H27" s="7" t="str" cm="1">
         <f t="array" ref="H27:L27">TRANSPOSE($H$2:$H$6)</f>
         <v>0-490</v>
@@ -2784,7 +2880,7 @@
         <f t="shared" si="0"/>
         <v>640-780</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="12" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="5" t="str" cm="1">
@@ -2823,7 +2919,7 @@
         <f t="shared" si="0"/>
         <v>780-880</v>
       </c>
-      <c r="F29" s="10"/>
+      <c r="F29" s="12"/>
       <c r="G29" s="5" t="str">
         <v>490-640</v>
       </c>
@@ -2859,7 +2955,7 @@
         <f t="shared" si="0"/>
         <v>880+</v>
       </c>
-      <c r="F30" s="10"/>
+      <c r="F30" s="12"/>
       <c r="G30" s="5" t="str">
         <v>640-780</v>
       </c>
@@ -2895,7 +2991,7 @@
         <f t="shared" si="0"/>
         <v>0-490</v>
       </c>
-      <c r="F31" s="10"/>
+      <c r="F31" s="12"/>
       <c r="G31" s="5" t="str">
         <v>780-880</v>
       </c>
@@ -2931,7 +3027,7 @@
         <f t="shared" si="0"/>
         <v>640-780</v>
       </c>
-      <c r="F32" s="10"/>
+      <c r="F32" s="12"/>
       <c r="G32" s="5" t="str">
         <v>880+</v>
       </c>
@@ -3618,6 +3714,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="N19:Q23"/>
     <mergeCell ref="H26:L26"/>
     <mergeCell ref="F28:F32"/>
     <mergeCell ref="F25:L25"/>
@@ -3626,7 +3723,6 @@
     <mergeCell ref="F10:F14"/>
     <mergeCell ref="H17:L17"/>
     <mergeCell ref="F19:F23"/>
-    <mergeCell ref="N19:Q23"/>
   </mergeCells>
   <conditionalFormatting sqref="H28:L32">
     <cfRule type="colorScale" priority="1">
@@ -3642,4 +3738,2829 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99450D20-3309-4EB4-8FC2-5072E6D2C8D3}">
+  <dimension ref="A1:R87"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="13"/>
+      <c r="I1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1941</v>
+      </c>
+      <c r="B2">
+        <v>780</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f t="shared" ref="C2:C65" si="0">LOOKUP(B2,$G$2:$G$6,$H$2:$H$6)</f>
+        <v>[720-875]</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF($C$2:$C$87,H2)</f>
+        <v>3</v>
+      </c>
+      <c r="J2" s="2">
+        <f>I2/SUM($I$2:$I$6)</f>
+        <v>3.4883720930232558E-2</v>
+      </c>
+      <c r="N2" t="str" cm="1">
+        <f t="array" ref="N2:N20">_xlfn._xlws.SORT(_xlfn.UNIQUE(D3:D87))</f>
+        <v>[0-273][0-273]</v>
+      </c>
+      <c r="O2">
+        <f>COUNTIF($D$3:$D$87,N2)</f>
+        <v>1</v>
+      </c>
+      <c r="P2" s="18">
+        <f>O2/SUM($O$2:$O$20)</f>
+        <v>1.1764705882352941E-2</v>
+      </c>
+      <c r="Q2">
+        <f>IF(P2=0,0,(P2-$R$2)^2)</f>
+        <v>1.6701013141120875E-3</v>
+      </c>
+      <c r="R2" s="18">
+        <f>1/COUNTA(_xlfn.ANCHORARRAY(N2))</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1942</v>
+      </c>
+      <c r="B3">
+        <v>470</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D3" t="str">
+        <f>C2&amp;C3</f>
+        <v>[720-875][273-552]</v>
+      </c>
+      <c r="G3">
+        <v>273</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I6" si="1">COUNTIF($C$2:$C$87,H3)</f>
+        <v>22</v>
+      </c>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3:J6" si="2">I3/SUM($I$2:$I$6)</f>
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="N3" t="str">
+        <v>[0-273][273-552]</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O20" si="3">COUNTIF($D$3:$D$87,N3)</f>
+        <v>2</v>
+      </c>
+      <c r="P3" s="18">
+        <f t="shared" ref="P3:P20" si="4">O3/SUM($O$2:$O$62)</f>
+        <v>2.3529411764705882E-2</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q20" si="5">IF(P3=0,0,(P3-$R$2)^2)</f>
+        <v>8.4693613472764024E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1943</v>
+      </c>
+      <c r="B4">
+        <v>690</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" ref="D4:D67" si="6">C3&amp;C4</f>
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="G4">
+        <v>552</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" si="2"/>
+        <v>0.2441860465116279</v>
+      </c>
+      <c r="N4" t="str">
+        <v>[273-552][0-273]</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="P4" s="18">
+        <f t="shared" si="4"/>
+        <v>2.3529411764705882E-2</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="5"/>
+        <v>8.4693613472764024E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1944</v>
+      </c>
+      <c r="B5">
+        <v>640</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="G5">
+        <v>720</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="2"/>
+        <v>0.2441860465116279</v>
+      </c>
+      <c r="N5" t="str">
+        <v>[273-552][273-552]</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P5" s="18">
+        <f t="shared" si="4"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="5"/>
+        <v>3.8340250553537392E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>1945</v>
+      </c>
+      <c r="B6">
+        <v>790</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="G6">
+        <v>875</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" si="2"/>
+        <v>0.22093023255813954</v>
+      </c>
+      <c r="N6" t="str">
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P6" s="18">
+        <f t="shared" si="4"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="5"/>
+        <v>3.8340250553537392E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>1946</v>
+      </c>
+      <c r="B7">
+        <v>835</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][720-875]</v>
+      </c>
+      <c r="N7" t="str">
+        <v>[273-552][720-875]</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P7" s="18">
+        <f t="shared" si="4"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="5"/>
+        <v>3.8340250553537392E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>1947</v>
+      </c>
+      <c r="B8">
+        <v>530</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][273-552]</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="N8" t="str">
+        <v>[273-552][875+]</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P8" s="18">
+        <f t="shared" si="4"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="5"/>
+        <v>3.8340250553537392E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>1948</v>
+      </c>
+      <c r="B9">
+        <v>360</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][273-552]</v>
+      </c>
+      <c r="H9" s="11" t="str" cm="1">
+        <f t="array" ref="H9:L9">TRANSPOSE($H$2:$H$6)</f>
+        <v>[0-273]</v>
+      </c>
+      <c r="I9" s="11" t="str">
+        <v>[273-552]</v>
+      </c>
+      <c r="J9" s="11" t="str">
+        <v>[552-720]</v>
+      </c>
+      <c r="K9" s="11" t="str">
+        <v>[720-875]</v>
+      </c>
+      <c r="L9" s="11" t="str">
+        <v>[875+]</v>
+      </c>
+      <c r="N9" t="str">
+        <v>[552-720][273-552]</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="P9" s="18">
+        <f t="shared" si="4"/>
+        <v>4.7058823529411764E-2</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="5"/>
+        <v>3.105560294836524E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>1949</v>
+      </c>
+      <c r="B10">
+        <v>185</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[0-273]</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][0-273]</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="5" t="str" cm="1">
+        <f t="array" ref="G10:G28">_xlfn.ANCHORARRAY(N2)</f>
+        <v>[0-273][0-273]</v>
+      </c>
+      <c r="H10" cm="1">
+        <f t="array" ref="H10">SUM(($D$3:$D$86=$G10)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I10" cm="1">
+        <f t="array" ref="I10">SUM(($D$3:$D$86=$G10)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J10" cm="1">
+        <f t="array" ref="J10">SUM(($D$3:$D$86=$G10)*($C$4:$C$87=J$9))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" cm="1">
+        <f t="array" ref="K10">SUM(($D$3:$D$86=$G10)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L10" cm="1">
+        <f t="array" ref="L10">SUM(($D$3:$D$86=$G10)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="N10" t="str">
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="P10" s="18">
+        <f t="shared" si="4"/>
+        <v>7.0588235294117646E-2</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="5"/>
+        <v>3.2244150715524935E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>1950</v>
+      </c>
+      <c r="B11">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[0-273]</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="6"/>
+        <v>[0-273][0-273]</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="5" t="str">
+        <v>[0-273][273-552]</v>
+      </c>
+      <c r="H11" cm="1">
+        <f t="array" ref="H11">SUM(($D$3:$D$86=$G11)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I11" cm="1">
+        <f t="array" ref="I11">SUM(($D$3:$D$86=$G11)*($C$4:$C$87=I$9))</f>
+        <v>0</v>
+      </c>
+      <c r="J11" cm="1">
+        <f t="array" ref="J11">SUM(($D$3:$D$86=$G11)*($C$4:$C$87=J$9))</f>
+        <v>1</v>
+      </c>
+      <c r="K11" cm="1">
+        <f t="array" ref="K11">SUM(($D$3:$D$86=$G11)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L11" cm="1">
+        <f t="array" ref="L11">SUM(($D$3:$D$86=$G11)*($C$4:$C$87=L$9))</f>
+        <v>1</v>
+      </c>
+      <c r="N11" t="str">
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="P11" s="18">
+        <f t="shared" si="4"/>
+        <v>9.4117647058823528E-2</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="5"/>
+        <v>1.7210938473482926E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>1951</v>
+      </c>
+      <c r="B12">
+        <v>430</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="6"/>
+        <v>[0-273][273-552]</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="5" t="str">
+        <v>[273-552][0-273]</v>
+      </c>
+      <c r="H12" cm="1">
+        <f t="array" ref="H12">SUM(($D$3:$D$86=$G12)*($C$4:$C$87=H$9))</f>
+        <v>1</v>
+      </c>
+      <c r="I12" cm="1">
+        <f t="array" ref="I12">SUM(($D$3:$D$86=$G12)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J12" cm="1">
+        <f t="array" ref="J12">SUM(($D$3:$D$86=$G12)*($C$4:$C$87=J$9))</f>
+        <v>0</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">SUM(($D$3:$D$86=$G12)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L12" cm="1">
+        <f t="array" ref="L12">SUM(($D$3:$D$86=$G12)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="N12" t="str">
+        <v>[552-720][875+]</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="P12" s="18">
+        <f t="shared" si="4"/>
+        <v>3.5294117647058823E-2</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="5"/>
+        <v>3.0058756433973288E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>1952</v>
+      </c>
+      <c r="B13">
+        <v>620</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="5" t="str">
+        <v>[273-552][273-552]</v>
+      </c>
+      <c r="H13" cm="1">
+        <f t="array" ref="H13">SUM(($D$3:$D$86=$G13)*($C$4:$C$87=H$9))</f>
+        <v>1</v>
+      </c>
+      <c r="I13" cm="1">
+        <f t="array" ref="I13">SUM(($D$3:$D$86=$G13)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J13" cm="1">
+        <f t="array" ref="J13">SUM(($D$3:$D$86=$G13)*($C$4:$C$87=J$9))</f>
+        <v>1</v>
+      </c>
+      <c r="K13" cm="1">
+        <f t="array" ref="K13">SUM(($D$3:$D$86=$G13)*($C$4:$C$87=K$9))</f>
+        <v>2</v>
+      </c>
+      <c r="L13" cm="1">
+        <f t="array" ref="L13">SUM(($D$3:$D$86=$G13)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="N13" t="str">
+        <v>[720-875][273-552]</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P13" s="18">
+        <f t="shared" si="4"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="5"/>
+        <v>3.8340250553537392E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>1953</v>
+      </c>
+      <c r="B14">
+        <v>790</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="5" t="str">
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="H14" cm="1">
+        <f t="array" ref="H14">SUM(($D$3:$D$86=$G14)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I14" cm="1">
+        <f t="array" ref="I14">SUM(($D$3:$D$86=$G14)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J14" cm="1">
+        <f t="array" ref="J14">SUM(($D$3:$D$86=$G14)*($C$4:$C$87=J$9))</f>
+        <v>2</v>
+      </c>
+      <c r="K14" cm="1">
+        <f t="array" ref="K14">SUM(($D$3:$D$86=$G14)*($C$4:$C$87=K$9))</f>
+        <v>2</v>
+      </c>
+      <c r="L14" cm="1">
+        <f t="array" ref="L14">SUM(($D$3:$D$86=$G14)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="N14" t="str">
+        <v>[720-875][552-720]</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="P14" s="18">
+        <f t="shared" si="4"/>
+        <v>7.0588235294117646E-2</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="5"/>
+        <v>3.2244150715524935E-4</v>
+      </c>
+      <c r="R14" s="19">
+        <f>SUM(Q2:Q62)*1000</f>
+        <v>7.8528501183755246</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>1954</v>
+      </c>
+      <c r="B15">
+        <v>880</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][875+]</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="5" t="str">
+        <v>[273-552][720-875]</v>
+      </c>
+      <c r="H15" cm="1">
+        <f t="array" ref="H15">SUM(($D$3:$D$86=$G15)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I15" cm="1">
+        <f t="array" ref="I15">SUM(($D$3:$D$86=$G15)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J15" cm="1">
+        <f t="array" ref="J15">SUM(($D$3:$D$86=$G15)*($C$4:$C$87=J$9))</f>
+        <v>2</v>
+      </c>
+      <c r="K15" cm="1">
+        <f t="array" ref="K15">SUM(($D$3:$D$86=$G15)*($C$4:$C$87=K$9))</f>
+        <v>2</v>
+      </c>
+      <c r="L15" cm="1">
+        <f t="array" ref="L15">SUM(($D$3:$D$86=$G15)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="N15" t="str">
+        <v>[720-875][720-875]</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P15" s="18">
+        <f t="shared" si="4"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="5"/>
+        <v>3.8340250553537392E-5</v>
+      </c>
+      <c r="R15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>1955</v>
+      </c>
+      <c r="B16">
+        <v>560</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][552-720]</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="5" t="str">
+        <v>[273-552][875+]</v>
+      </c>
+      <c r="H16" cm="1">
+        <f t="array" ref="H16">SUM(($D$3:$D$86=$G16)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I16" cm="1">
+        <f t="array" ref="I16">SUM(($D$3:$D$86=$G16)*($C$4:$C$87=I$9))</f>
+        <v>2</v>
+      </c>
+      <c r="J16" cm="1">
+        <f t="array" ref="J16">SUM(($D$3:$D$86=$G16)*($C$4:$C$87=J$9))</f>
+        <v>0</v>
+      </c>
+      <c r="K16" cm="1">
+        <f t="array" ref="K16">SUM(($D$3:$D$86=$G16)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L16" cm="1">
+        <f t="array" ref="L16">SUM(($D$3:$D$86=$G16)*($C$4:$C$87=L$9))</f>
+        <v>2</v>
+      </c>
+      <c r="N16" t="str">
+        <v>[720-875][875+]</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P16" s="18">
+        <f t="shared" si="4"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="5"/>
+        <v>3.8340250553537392E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>1956</v>
+      </c>
+      <c r="B17">
+        <v>455</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][273-552]</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="5" t="str">
+        <v>[552-720][273-552]</v>
+      </c>
+      <c r="H17" cm="1">
+        <f t="array" ref="H17">SUM(($D$3:$D$86=$G17)*($C$4:$C$87=H$9))</f>
+        <v>1</v>
+      </c>
+      <c r="I17" cm="1">
+        <f t="array" ref="I17">SUM(($D$3:$D$86=$G17)*($C$4:$C$87=I$9))</f>
+        <v>0</v>
+      </c>
+      <c r="J17" cm="1">
+        <f t="array" ref="J17">SUM(($D$3:$D$86=$G17)*($C$4:$C$87=J$9))</f>
+        <v>0</v>
+      </c>
+      <c r="K17" cm="1">
+        <f t="array" ref="K17">SUM(($D$3:$D$86=$G17)*($C$4:$C$87=K$9))</f>
+        <v>2</v>
+      </c>
+      <c r="L17" cm="1">
+        <f t="array" ref="L17">SUM(($D$3:$D$86=$G17)*($C$4:$C$87=L$9))</f>
+        <v>1</v>
+      </c>
+      <c r="N17" t="str">
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="P17" s="18">
+        <f t="shared" si="4"/>
+        <v>7.0588235294117646E-2</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="5"/>
+        <v>3.2244150715524935E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>1957</v>
+      </c>
+      <c r="B18">
+        <v>1240</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][875+]</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="5" t="str">
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="H18" cm="1">
+        <f t="array" ref="H18">SUM(($D$3:$D$86=$G18)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I18" cm="1">
+        <f t="array" ref="I18">SUM(($D$3:$D$86=$G18)*($C$4:$C$87=I$9))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" cm="1">
+        <f t="array" ref="J18">SUM(($D$3:$D$86=$G18)*($C$4:$C$87=J$9))</f>
+        <v>2</v>
+      </c>
+      <c r="K18" cm="1">
+        <f t="array" ref="K18">SUM(($D$3:$D$86=$G18)*($C$4:$C$87=K$9))</f>
+        <v>3</v>
+      </c>
+      <c r="L18" cm="1">
+        <f t="array" ref="L18">SUM(($D$3:$D$86=$G18)*($C$4:$C$87=L$9))</f>
+        <v>1</v>
+      </c>
+      <c r="N18" t="str">
+        <v>[875+][552-720]</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="P18" s="18">
+        <f t="shared" si="4"/>
+        <v>4.7058823529411764E-2</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="5"/>
+        <v>3.105560294836524E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>1958</v>
+      </c>
+      <c r="B19">
+        <v>410</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="5" t="str">
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="H19" cm="1">
+        <f t="array" ref="H19">SUM(($D$3:$D$86=$G19)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I19" cm="1">
+        <f t="array" ref="I19">SUM(($D$3:$D$86=$G19)*($C$4:$C$87=I$9))</f>
+        <v>0</v>
+      </c>
+      <c r="J19" cm="1">
+        <f t="array" ref="J19">SUM(($D$3:$D$86=$G19)*($C$4:$C$87=J$9))</f>
+        <v>1</v>
+      </c>
+      <c r="K19" cm="1">
+        <f t="array" ref="K19">SUM(($D$3:$D$86=$G19)*($C$4:$C$87=K$9))</f>
+        <v>3</v>
+      </c>
+      <c r="L19" cm="1">
+        <f t="array" ref="L19">SUM(($D$3:$D$86=$G19)*($C$4:$C$87=L$9))</f>
+        <v>4</v>
+      </c>
+      <c r="N19" s="17" t="str">
+        <v>[875+][720-875]</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="P19" s="18">
+        <f t="shared" si="4"/>
+        <v>2.3529411764705882E-2</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="5"/>
+        <v>8.4693613472764024E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>1959</v>
+      </c>
+      <c r="B20">
+        <v>580</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="5" t="str">
+        <v>[552-720][875+]</v>
+      </c>
+      <c r="H20" cm="1">
+        <f t="array" ref="H20">SUM(($D$3:$D$86=$G20)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I20" cm="1">
+        <f t="array" ref="I20">SUM(($D$3:$D$86=$G20)*($C$4:$C$87=I$9))</f>
+        <v>0</v>
+      </c>
+      <c r="J20" cm="1">
+        <f t="array" ref="J20">SUM(($D$3:$D$86=$G20)*($C$4:$C$87=J$9))</f>
+        <v>2</v>
+      </c>
+      <c r="K20" cm="1">
+        <f t="array" ref="K20">SUM(($D$3:$D$86=$G20)*($C$4:$C$87=K$9))</f>
+        <v>1</v>
+      </c>
+      <c r="L20" cm="1">
+        <f t="array" ref="L20">SUM(($D$3:$D$86=$G20)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="17" t="str">
+        <v>[875+][875+]</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="P20" s="18">
+        <f t="shared" si="4"/>
+        <v>7.0588235294117646E-2</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="5"/>
+        <v>3.2244150715524935E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>1960</v>
+      </c>
+      <c r="B21">
+        <v>490</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][273-552]</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="5" t="str">
+        <v>[720-875][273-552]</v>
+      </c>
+      <c r="H21" cm="1">
+        <f t="array" ref="H21">SUM(($D$3:$D$86=$G21)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I21" cm="1">
+        <f t="array" ref="I21">SUM(($D$3:$D$86=$G21)*($C$4:$C$87=I$9))</f>
+        <v>2</v>
+      </c>
+      <c r="J21" cm="1">
+        <f t="array" ref="J21">SUM(($D$3:$D$86=$G21)*($C$4:$C$87=J$9))</f>
+        <v>1</v>
+      </c>
+      <c r="K21" cm="1">
+        <f t="array" ref="K21">SUM(($D$3:$D$86=$G21)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L21" cm="1">
+        <f t="array" ref="L21">SUM(($D$3:$D$86=$G21)*($C$4:$C$87=L$9))</f>
+        <v>2</v>
+      </c>
+      <c r="N21" s="17"/>
+      <c r="P21" s="18"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>1961</v>
+      </c>
+      <c r="B22">
+        <v>820</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][720-875]</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="5" t="str">
+        <v>[720-875][552-720]</v>
+      </c>
+      <c r="H22" cm="1">
+        <f t="array" ref="H22">SUM(($D$3:$D$86=$G22)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I22" cm="1">
+        <f t="array" ref="I22">SUM(($D$3:$D$86=$G22)*($C$4:$C$87=I$9))</f>
+        <v>2</v>
+      </c>
+      <c r="J22" cm="1">
+        <f t="array" ref="J22">SUM(($D$3:$D$86=$G22)*($C$4:$C$87=J$9))</f>
+        <v>2</v>
+      </c>
+      <c r="K22" cm="1">
+        <f t="array" ref="K22">SUM(($D$3:$D$86=$G22)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L22" cm="1">
+        <f t="array" ref="L22">SUM(($D$3:$D$86=$G22)*($C$4:$C$87=L$9))</f>
+        <v>2</v>
+      </c>
+      <c r="N22" s="17"/>
+      <c r="P22" s="18"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>1962</v>
+      </c>
+      <c r="B23">
+        <v>530</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][273-552]</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="5" t="str">
+        <v>[720-875][720-875]</v>
+      </c>
+      <c r="H23" cm="1">
+        <f t="array" ref="H23">SUM(($D$3:$D$86=$G23)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I23" cm="1">
+        <f t="array" ref="I23">SUM(($D$3:$D$86=$G23)*($C$4:$C$87=I$9))</f>
+        <v>2</v>
+      </c>
+      <c r="J23" cm="1">
+        <f t="array" ref="J23">SUM(($D$3:$D$86=$G23)*($C$4:$C$87=J$9))</f>
+        <v>2</v>
+      </c>
+      <c r="K23" cm="1">
+        <f t="array" ref="K23">SUM(($D$3:$D$86=$G23)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L23" cm="1">
+        <f t="array" ref="L23">SUM(($D$3:$D$86=$G23)*($C$4:$C$87=L$9))</f>
+        <v>1</v>
+      </c>
+      <c r="N23" s="17"/>
+      <c r="P23" s="18"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>1963</v>
+      </c>
+      <c r="B24">
+        <v>980</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][875+]</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="5" t="str">
+        <v>[720-875][875+]</v>
+      </c>
+      <c r="H24" cm="1">
+        <f t="array" ref="H24">SUM(($D$3:$D$86=$G24)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I24" cm="1">
+        <f t="array" ref="I24">SUM(($D$3:$D$86=$G24)*($C$4:$C$87=I$9))</f>
+        <v>3</v>
+      </c>
+      <c r="J24" cm="1">
+        <f t="array" ref="J24">SUM(($D$3:$D$86=$G24)*($C$4:$C$87=J$9))</f>
+        <v>1</v>
+      </c>
+      <c r="K24" cm="1">
+        <f t="array" ref="K24">SUM(($D$3:$D$86=$G24)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L24" cm="1">
+        <f t="array" ref="L24">SUM(($D$3:$D$86=$G24)*($C$4:$C$87=L$9))</f>
+        <v>1</v>
+      </c>
+      <c r="P24" s="18"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>1964</v>
+      </c>
+      <c r="B25">
+        <v>490</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="5" t="str">
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="H25" cm="1">
+        <f t="array" ref="H25">SUM(($D$3:$D$86=$G25)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I25" cm="1">
+        <f t="array" ref="I25">SUM(($D$3:$D$86=$G25)*($C$4:$C$87=I$9))</f>
+        <v>2</v>
+      </c>
+      <c r="J25" cm="1">
+        <f t="array" ref="J25">SUM(($D$3:$D$86=$G25)*($C$4:$C$87=J$9))</f>
+        <v>2</v>
+      </c>
+      <c r="K25" cm="1">
+        <f t="array" ref="K25">SUM(($D$3:$D$86=$G25)*($C$4:$C$87=K$9))</f>
+        <v>1</v>
+      </c>
+      <c r="L25" cm="1">
+        <f t="array" ref="L25">SUM(($D$3:$D$86=$G25)*($C$4:$C$87=L$9))</f>
+        <v>1</v>
+      </c>
+      <c r="P25" s="18"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>1965</v>
+      </c>
+      <c r="B26">
+        <v>490</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][273-552]</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="5" t="str">
+        <v>[875+][552-720]</v>
+      </c>
+      <c r="H26" cm="1">
+        <f t="array" ref="H26">SUM(($D$3:$D$86=$G26)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I26" cm="1">
+        <f t="array" ref="I26">SUM(($D$3:$D$86=$G26)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J26" cm="1">
+        <f t="array" ref="J26">SUM(($D$3:$D$86=$G26)*($C$4:$C$87=J$9))</f>
+        <v>0</v>
+      </c>
+      <c r="K26" cm="1">
+        <f t="array" ref="K26">SUM(($D$3:$D$86=$G26)*($C$4:$C$87=K$9))</f>
+        <v>3</v>
+      </c>
+      <c r="L26" cm="1">
+        <f t="array" ref="L26">SUM(($D$3:$D$86=$G26)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="18"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>1966</v>
+      </c>
+      <c r="B27">
+        <v>385</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][273-552]</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="5" t="str">
+        <v>[875+][720-875]</v>
+      </c>
+      <c r="H27" cm="1">
+        <f t="array" ref="H27">SUM(($D$3:$D$86=$G27)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I27" cm="1">
+        <f t="array" ref="I27">SUM(($D$3:$D$86=$G27)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J27" cm="1">
+        <f t="array" ref="J27">SUM(($D$3:$D$86=$G27)*($C$4:$C$87=J$9))</f>
+        <v>1</v>
+      </c>
+      <c r="K27" cm="1">
+        <f t="array" ref="K27">SUM(($D$3:$D$86=$G27)*($C$4:$C$87=K$9))</f>
+        <v>0</v>
+      </c>
+      <c r="L27" cm="1">
+        <f t="array" ref="L27">SUM(($D$3:$D$86=$G27)*($C$4:$C$87=L$9))</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="18"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>1967</v>
+      </c>
+      <c r="B28">
+        <v>670</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="5" t="str">
+        <v>[875+][875+]</v>
+      </c>
+      <c r="H28" cm="1">
+        <f t="array" ref="H28">SUM(($D$3:$D$86=$G28)*($C$4:$C$87=H$9))</f>
+        <v>0</v>
+      </c>
+      <c r="I28" cm="1">
+        <f t="array" ref="I28">SUM(($D$3:$D$86=$G28)*($C$4:$C$87=I$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J28" cm="1">
+        <f t="array" ref="J28">SUM(($D$3:$D$86=$G28)*($C$4:$C$87=J$9))</f>
+        <v>1</v>
+      </c>
+      <c r="K28" cm="1">
+        <f t="array" ref="K28">SUM(($D$3:$D$86=$G28)*($C$4:$C$87=K$9))</f>
+        <v>1</v>
+      </c>
+      <c r="L28" cm="1">
+        <f t="array" ref="L28">SUM(($D$3:$D$86=$G28)*($C$4:$C$87=L$9))</f>
+        <v>3</v>
+      </c>
+      <c r="P28" s="18"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>1968</v>
+      </c>
+      <c r="B29">
+        <v>795</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="P29" s="18"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>1969</v>
+      </c>
+      <c r="B30">
+        <v>1135</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][875+]</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="P30" s="18"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>1970</v>
+      </c>
+      <c r="B31">
+        <v>430</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="H31" s="11" t="str" cm="1">
+        <f t="array" ref="H31:L31">TRANSPOSE($H$2:$H$6)</f>
+        <v>[0-273]</v>
+      </c>
+      <c r="I31" s="11" t="str">
+        <v>[273-552]</v>
+      </c>
+      <c r="J31" s="11" t="str">
+        <v>[552-720]</v>
+      </c>
+      <c r="K31" s="11" t="str">
+        <v>[720-875]</v>
+      </c>
+      <c r="L31" s="11" t="str">
+        <v>[875+]</v>
+      </c>
+      <c r="P31" s="18"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>1971</v>
+      </c>
+      <c r="B32">
+        <v>770</v>
+      </c>
+      <c r="C32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][720-875]</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="5" t="str" cm="1">
+        <f t="array" ref="G32:G50">_xlfn.ANCHORARRAY(N2)</f>
+        <v>[0-273][0-273]</v>
+      </c>
+      <c r="H32" s="18">
+        <f>H10/SUM($H10:$L10)-$R$2</f>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I32" s="18">
+        <f t="shared" ref="I32:L32" si="7">I10/SUM($H10:$L10)-$R$2</f>
+        <v>0.94736842105263164</v>
+      </c>
+      <c r="J32" s="18">
+        <f t="shared" si="7"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="K32" s="18">
+        <f t="shared" si="7"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L32" s="18">
+        <f t="shared" si="7"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P32" s="18"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>1972</v>
+      </c>
+      <c r="B33">
+        <v>820</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][720-875]</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="5" t="str">
+        <v>[0-273][273-552]</v>
+      </c>
+      <c r="H33" s="18">
+        <f t="shared" ref="H33:L48" si="8">H11/SUM($H11:$L11)-$R$2</f>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I33" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="J33" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="K33" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L33" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="P33" s="18"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>1973</v>
+      </c>
+      <c r="B34">
+        <v>585</v>
+      </c>
+      <c r="C34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][552-720]</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="5" t="str">
+        <v>[273-552][0-273]</v>
+      </c>
+      <c r="H34" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="J34" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="K34" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L34" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P34" s="18"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>1974</v>
+      </c>
+      <c r="B35">
+        <v>995</v>
+      </c>
+      <c r="C35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][875+]</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="5" t="str">
+        <v>[273-552][273-552]</v>
+      </c>
+      <c r="H35" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="I35" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="J35" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="K35" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="L35" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P35" s="18"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>1975</v>
+      </c>
+      <c r="B36">
+        <v>660</v>
+      </c>
+      <c r="C36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][552-720]</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="5" t="str">
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="H36" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I36" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="J36" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="K36" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="L36" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P36" s="18"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>1976</v>
+      </c>
+      <c r="B37">
+        <v>750</v>
+      </c>
+      <c r="C37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="5" t="str">
+        <v>[273-552][720-875]</v>
+      </c>
+      <c r="H37" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="J37" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="K37" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="L37" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P37" s="18"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>1977</v>
+      </c>
+      <c r="B38">
+        <v>650</v>
+      </c>
+      <c r="C38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][552-720]</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="5" t="str">
+        <v>[273-552][875+]</v>
+      </c>
+      <c r="H38" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I38" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="J38" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="K38" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L38" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="P38" s="18"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>1978</v>
+      </c>
+      <c r="B39">
+        <v>700</v>
+      </c>
+      <c r="C39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="5" t="str">
+        <v>[552-720][273-552]</v>
+      </c>
+      <c r="H39" s="18">
+        <f t="shared" si="8"/>
+        <v>0.19736842105263158</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="J39" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="K39" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="L39" s="18">
+        <f t="shared" si="8"/>
+        <v>0.19736842105263158</v>
+      </c>
+      <c r="P39" s="18"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B40">
+        <v>680</v>
+      </c>
+      <c r="C40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="5" t="str">
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="H40" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I40" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="J40" s="18">
+        <f t="shared" si="8"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="K40" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="L40" s="18">
+        <f t="shared" si="8"/>
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="P40" s="18"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B41">
+        <v>570</v>
+      </c>
+      <c r="C41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="5" t="str">
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="H41" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I41" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="J41" s="18">
+        <f t="shared" si="8"/>
+        <v>7.2368421052631582E-2</v>
+      </c>
+      <c r="K41" s="18">
+        <f t="shared" si="8"/>
+        <v>0.32236842105263158</v>
+      </c>
+      <c r="L41" s="18">
+        <f t="shared" si="8"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="P41" s="18"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B42">
+        <v>780</v>
+      </c>
+      <c r="C42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="5" t="str">
+        <v>[552-720][875+]</v>
+      </c>
+      <c r="H42" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I42" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="J42" s="18">
+        <f t="shared" si="8"/>
+        <v>0.61403508771929816</v>
+      </c>
+      <c r="K42" s="18">
+        <f t="shared" si="8"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="L42" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P42" s="18"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B43">
+        <v>970</v>
+      </c>
+      <c r="C43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][875+]</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="5" t="str">
+        <v>[720-875][273-552]</v>
+      </c>
+      <c r="H43" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I43" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="J43" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="K43" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L43" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="P43" s="18"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B44">
+        <v>485</v>
+      </c>
+      <c r="C44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="5" t="str">
+        <v>[720-875][552-720]</v>
+      </c>
+      <c r="H44" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I44" s="18">
+        <f t="shared" si="8"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="J44" s="18">
+        <f t="shared" si="8"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="K44" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L44" s="18">
+        <f t="shared" si="8"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="P44" s="18"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>1984</v>
+      </c>
+      <c r="B45">
+        <v>705</v>
+      </c>
+      <c r="C45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][552-720]</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="5" t="str">
+        <v>[720-875][720-875]</v>
+      </c>
+      <c r="H45" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I45" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="J45" s="18">
+        <f t="shared" si="8"/>
+        <v>0.3473684210526316</v>
+      </c>
+      <c r="K45" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L45" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="P45" s="18"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>1985</v>
+      </c>
+      <c r="B46">
+        <v>715</v>
+      </c>
+      <c r="C46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][552-720]</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="5" t="str">
+        <v>[720-875][875+]</v>
+      </c>
+      <c r="H46" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I46" s="18">
+        <f t="shared" si="8"/>
+        <v>0.5473684210526315</v>
+      </c>
+      <c r="J46" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="K46" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L46" s="18">
+        <f t="shared" si="8"/>
+        <v>0.14736842105263159</v>
+      </c>
+      <c r="P46" s="18"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>1986</v>
+      </c>
+      <c r="B47">
+        <v>725</v>
+      </c>
+      <c r="C47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="5" t="str">
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="H47" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I47" s="18">
+        <f t="shared" si="8"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="J47" s="18">
+        <f t="shared" si="8"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="K47" s="18">
+        <f t="shared" si="8"/>
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="L47" s="18">
+        <f t="shared" si="8"/>
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="P47" s="18"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>1987</v>
+      </c>
+      <c r="B48">
+        <v>750</v>
+      </c>
+      <c r="C48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][720-875]</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="5" t="str">
+        <v>[875+][552-720]</v>
+      </c>
+      <c r="H48" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I48" s="18">
+        <f t="shared" si="8"/>
+        <v>0.19736842105263158</v>
+      </c>
+      <c r="J48" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="K48" s="18">
+        <f t="shared" si="8"/>
+        <v>0.69736842105263164</v>
+      </c>
+      <c r="L48" s="18">
+        <f t="shared" si="8"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P48" s="18"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>1988</v>
+      </c>
+      <c r="B49">
+        <v>902</v>
+      </c>
+      <c r="C49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][875+]</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="5" t="str">
+        <v>[875+][720-875]</v>
+      </c>
+      <c r="H49" s="18">
+        <f t="shared" ref="H49:L50" si="9">H27/SUM($H27:$L27)-$R$2</f>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I49" s="18">
+        <f t="shared" si="9"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="J49" s="18">
+        <f t="shared" si="9"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="K49" s="18">
+        <f t="shared" si="9"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="L49" s="18">
+        <f t="shared" si="9"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="P49" s="18"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>1989</v>
+      </c>
+      <c r="B50">
+        <v>498</v>
+      </c>
+      <c r="C50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][273-552]</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="5" t="str">
+        <v>[875+][875+]</v>
+      </c>
+      <c r="H50" s="18">
+        <f t="shared" si="9"/>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="I50" s="18">
+        <f t="shared" si="9"/>
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="J50" s="18">
+        <f t="shared" si="9"/>
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="K50" s="18">
+        <f t="shared" si="9"/>
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="L50" s="18">
+        <f t="shared" si="9"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="P50" s="18"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>1990</v>
+      </c>
+      <c r="B51">
+        <v>945</v>
+      </c>
+      <c r="C51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][875+]</v>
+      </c>
+      <c r="P51" s="18"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>1991</v>
+      </c>
+      <c r="B52">
+        <v>935</v>
+      </c>
+      <c r="C52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][875+]</v>
+      </c>
+      <c r="P52" s="18"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>1992</v>
+      </c>
+      <c r="B53">
+        <v>1002</v>
+      </c>
+      <c r="C53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][875+]</v>
+      </c>
+      <c r="P53" s="18"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>1993</v>
+      </c>
+      <c r="B54">
+        <v>880</v>
+      </c>
+      <c r="C54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][875+]</v>
+      </c>
+      <c r="P54" s="18"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>1994</v>
+      </c>
+      <c r="B55">
+        <v>960</v>
+      </c>
+      <c r="C55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][875+]</v>
+      </c>
+      <c r="P55" s="18"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>1995</v>
+      </c>
+      <c r="B56">
+        <v>665</v>
+      </c>
+      <c r="C56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][552-720]</v>
+      </c>
+      <c r="P56" s="18"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>1996</v>
+      </c>
+      <c r="B57">
+        <v>780</v>
+      </c>
+      <c r="C57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][720-875]</v>
+      </c>
+      <c r="P57" s="18"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>1997</v>
+      </c>
+      <c r="B58">
+        <v>850</v>
+      </c>
+      <c r="C58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][720-875]</v>
+      </c>
+      <c r="P58" s="18"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>1998</v>
+      </c>
+      <c r="B59">
+        <v>620</v>
+      </c>
+      <c r="C59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][552-720]</v>
+      </c>
+      <c r="P59" s="18"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>1999</v>
+      </c>
+      <c r="B60">
+        <v>330</v>
+      </c>
+      <c r="C60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][273-552]</v>
+      </c>
+      <c r="P60" s="18"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>2000</v>
+      </c>
+      <c r="B61">
+        <v>270</v>
+      </c>
+      <c r="C61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[0-273]</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][0-273]</v>
+      </c>
+      <c r="P61" s="18"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B62">
+        <v>510</v>
+      </c>
+      <c r="C62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="6"/>
+        <v>[0-273][273-552]</v>
+      </c>
+      <c r="P62" s="18"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>2002</v>
+      </c>
+      <c r="B63">
+        <v>930</v>
+      </c>
+      <c r="C63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="6"/>
+        <v>[273-552][875+]</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>2003</v>
+      </c>
+      <c r="B64">
+        <v>875</v>
+      </c>
+      <c r="C64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][875+]</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>2004</v>
+      </c>
+      <c r="B65">
+        <v>840</v>
+      </c>
+      <c r="C65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="6"/>
+        <v>[875+][720-875]</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B66">
+        <v>630</v>
+      </c>
+      <c r="C66" s="1" t="str">
+        <f t="shared" ref="C66:C87" si="10">LOOKUP(B66,$G$2:$G$6,$H$2:$H$6)</f>
+        <v>[552-720]</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="6"/>
+        <v>[720-875][552-720]</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B67">
+        <v>875</v>
+      </c>
+      <c r="C67" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="6"/>
+        <v>[552-720][875+]</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B68">
+        <v>874</v>
+      </c>
+      <c r="C68" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" ref="D68:D87" si="11">C67&amp;C68</f>
+        <v>[875+][720-875]</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B69">
+        <v>307</v>
+      </c>
+      <c r="C69" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="11"/>
+        <v>[720-875][273-552]</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B70">
+        <v>415</v>
+      </c>
+      <c r="C70" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="11"/>
+        <v>[273-552][273-552]</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>2010</v>
+      </c>
+      <c r="B71">
+        <v>844</v>
+      </c>
+      <c r="C71" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="11"/>
+        <v>[273-552][720-875]</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>2011</v>
+      </c>
+      <c r="B72">
+        <v>661</v>
+      </c>
+      <c r="C72" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="11"/>
+        <v>[720-875][552-720]</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>2012</v>
+      </c>
+      <c r="B73">
+        <v>547</v>
+      </c>
+      <c r="C73" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="11"/>
+        <v>[552-720][273-552]</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>2013</v>
+      </c>
+      <c r="B74">
+        <v>826</v>
+      </c>
+      <c r="C74" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="11"/>
+        <v>[273-552][720-875]</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>2014</v>
+      </c>
+      <c r="B75">
+        <v>581</v>
+      </c>
+      <c r="C75" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D75" t="str">
+        <f t="shared" si="11"/>
+        <v>[720-875][552-720]</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>2015</v>
+      </c>
+      <c r="B76">
+        <v>691</v>
+      </c>
+      <c r="C76" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D76" t="str">
+        <f t="shared" si="11"/>
+        <v>[552-720][552-720]</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>2016</v>
+      </c>
+      <c r="B77">
+        <v>947</v>
+      </c>
+      <c r="C77" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="11"/>
+        <v>[552-720][875+]</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>2017</v>
+      </c>
+      <c r="B78">
+        <v>561</v>
+      </c>
+      <c r="C78" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[552-720]</v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="11"/>
+        <v>[875+][552-720]</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>2018</v>
+      </c>
+      <c r="B79">
+        <v>850</v>
+      </c>
+      <c r="C79" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="11"/>
+        <v>[552-720][720-875]</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>2019</v>
+      </c>
+      <c r="B80">
+        <v>1618</v>
+      </c>
+      <c r="C80" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="11"/>
+        <v>[720-875][875+]</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>2020</v>
+      </c>
+      <c r="B81">
+        <v>931</v>
+      </c>
+      <c r="C81" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" si="11"/>
+        <v>[875+][875+]</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B82">
+        <v>401</v>
+      </c>
+      <c r="C82" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="11"/>
+        <v>[875+][273-552]</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B83">
+        <v>420</v>
+      </c>
+      <c r="C83" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="11"/>
+        <v>[273-552][273-552]</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B84">
+        <v>781</v>
+      </c>
+      <c r="C84" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="11"/>
+        <v>[273-552][720-875]</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B85">
+        <v>724</v>
+      </c>
+      <c r="C85" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[720-875]</v>
+      </c>
+      <c r="D85" t="str">
+        <f t="shared" si="11"/>
+        <v>[720-875][720-875]</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B86">
+        <v>350</v>
+      </c>
+      <c r="C86" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[273-552]</v>
+      </c>
+      <c r="D86" t="str">
+        <f t="shared" si="11"/>
+        <v>[720-875][273-552]</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B87">
+        <v>1070</v>
+      </c>
+      <c r="C87" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>[875+]</v>
+      </c>
+      <c r="D87" t="str">
+        <f t="shared" si="11"/>
+        <v>[273-552][875+]</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="F10:F28"/>
+    <mergeCell ref="H30:L30"/>
+    <mergeCell ref="F32:F50"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H32:L50">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>